--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B2">
-        <v>6100</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B3">
-        <v>6070</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B4">
-        <v>6050</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B5">
-        <v>6020</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B6">
-        <v>5990</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B7">
-        <v>5970</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B8">
-        <v>5970</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B9">
-        <v>5970</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B10">
-        <v>5970</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B11">
-        <v>5970</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B12">
-        <v>5970</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B13">
-        <v>5980</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B14">
-        <v>6000</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B15">
-        <v>6010</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B16">
-        <v>6030</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B17">
-        <v>6070</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B18">
-        <v>6150</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B19">
-        <v>6240</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B20">
-        <v>6350</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B21">
-        <v>6480</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B22">
-        <v>6630</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B23">
-        <v>6790</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B24">
-        <v>6940</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B25">
-        <v>7100</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B26">
-        <v>7250</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B27">
-        <v>7390</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B28">
-        <v>7490</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B29">
-        <v>7560</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B30">
-        <v>7620</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B31">
-        <v>7650</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B32">
-        <v>7650</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B33">
-        <v>7640</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B34">
-        <v>7590</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B35">
-        <v>7530</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B36">
-        <v>7470</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B37">
-        <v>7390</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B38">
-        <v>7310</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B39">
-        <v>7220</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B40">
-        <v>7140</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B41">
-        <v>7060</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B42">
-        <v>6990</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B43">
-        <v>6930</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B44">
-        <v>6890</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B45">
-        <v>6840</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B46">
-        <v>6790</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B47">
-        <v>6770</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B48">
-        <v>6770</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B49">
-        <v>6780</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B50">
-        <v>6800</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B51">
-        <v>6800</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B52">
-        <v>6800</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B53">
-        <v>6800</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B54">
-        <v>6800</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B55">
-        <v>6800</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B56">
-        <v>6810</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B57">
-        <v>6820</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B58">
-        <v>6860</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B59">
-        <v>6920</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B60">
-        <v>6990</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B61">
-        <v>7070</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B62">
-        <v>7160</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B63">
-        <v>7260</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B64">
-        <v>7370</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B65">
-        <v>7490</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B66">
-        <v>7600</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B67">
-        <v>7720</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B68">
-        <v>7830</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B69">
-        <v>7960</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B70">
-        <v>8100</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B71">
-        <v>8200</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B72">
-        <v>8270</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B73">
-        <v>8320</v>
+        <v>7470</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B74">
-        <v>8330</v>
+        <v>7590</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B75">
-        <v>8330</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B76">
-        <v>8330</v>
+        <v>7670</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B77">
-        <v>8320</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B78">
-        <v>8250</v>
+        <v>7630</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B79">
-        <v>8180</v>
+        <v>7590</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B80">
-        <v>8100</v>
+        <v>7520</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B81">
-        <v>8000</v>
+        <v>7470</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B82">
-        <v>7890</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B83">
-        <v>7780</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B84">
-        <v>7650</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B85">
-        <v>7520</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B86">
-        <v>7380</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B87">
-        <v>7230</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B88">
-        <v>7060</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B89">
-        <v>6930</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B90">
-        <v>6780</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B91">
-        <v>6660</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B92">
-        <v>6560</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B93">
-        <v>6460</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B94">
-        <v>6330</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B95">
-        <v>6280</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B96">
-        <v>6230</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B97">
-        <v>6180</v>
+        <v>5690</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B2">
         <v>5640</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B3">
         <v>5610</v>
@@ -410,279 +410,279 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B4">
-        <v>5590</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B5">
-        <v>5560</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B6">
-        <v>5540</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B7">
-        <v>5530</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B8">
-        <v>5520</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B9">
-        <v>5520</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B10">
-        <v>5520</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B11">
-        <v>5520</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B12">
-        <v>5530</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B13">
-        <v>5540</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B14">
-        <v>5560</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B15">
-        <v>5580</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B16">
-        <v>5620</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B17">
-        <v>5670</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B18">
-        <v>5750</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B19">
-        <v>5850</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B20">
-        <v>5950</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B21">
-        <v>6050</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B22">
-        <v>6170</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B23">
-        <v>6280</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B24">
-        <v>6370</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B25">
-        <v>6500</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B26">
-        <v>6650</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B27">
-        <v>6760</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B28">
-        <v>6810</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B29">
-        <v>6820</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B30">
-        <v>6790</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B31">
-        <v>6730</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B32">
-        <v>6640</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B33">
-        <v>6540</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B34">
-        <v>6400</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B35">
-        <v>6260</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B36">
-        <v>6110</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B37">
-        <v>5950</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B38">
         <v>5810</v>
@@ -690,474 +690,474 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B39">
-        <v>5660</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B40">
-        <v>5520</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B41">
-        <v>5400</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B42">
-        <v>5260</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B43">
-        <v>5160</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B44">
-        <v>5080</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B45">
-        <v>5000</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B46">
-        <v>4930</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B47">
-        <v>4880</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B48">
-        <v>4830</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B49">
-        <v>4810</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B50">
-        <v>4800</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B51">
-        <v>4780</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B52">
-        <v>4780</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B53">
-        <v>4780</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B54">
-        <v>4780</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B55">
-        <v>4800</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B56">
-        <v>4820</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B57">
-        <v>4860</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B58">
-        <v>4960</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B59">
-        <v>5080</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B60">
-        <v>5200</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B61">
-        <v>5370</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B62">
-        <v>5530</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B63">
-        <v>5710</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B64">
-        <v>5890</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B65">
-        <v>6080</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B66">
-        <v>6270</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B67">
-        <v>6460</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B68">
-        <v>6650</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B69">
-        <v>6830</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B70">
-        <v>7020</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B71">
-        <v>7190</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B72">
-        <v>7340</v>
+        <v>7290</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B73">
-        <v>7470</v>
+        <v>7420</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B74">
-        <v>7590</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B75">
-        <v>7650</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B76">
-        <v>7670</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B77">
-        <v>7660</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B78">
-        <v>7630</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B79">
-        <v>7590</v>
+        <v>7670</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B80">
-        <v>7520</v>
+        <v>7590</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B81">
-        <v>7470</v>
+        <v>7510</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B82">
-        <v>7360</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B83">
-        <v>7220</v>
+        <v>7290</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B84">
-        <v>7120</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B85">
-        <v>6980</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B86">
-        <v>6800</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B87">
-        <v>6650</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B88">
-        <v>6490</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B89">
-        <v>6350</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B90">
-        <v>6210</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B91">
-        <v>6090</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B92">
-        <v>5990</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B93">
-        <v>5880</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B94">
-        <v>5830</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B95">
-        <v>5770</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B96">
-        <v>5730</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B97">
-        <v>5690</v>
+        <v>5720</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,519 +394,519 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B2">
-        <v>5640</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46107.01041666666</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B3">
-        <v>5610</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46107.02083333334</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B4">
-        <v>5580</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46107.03125</v>
+        <v>46111.03125</v>
       </c>
       <c r="B5">
-        <v>5550</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46107.04166666666</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B6">
-        <v>5520</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46107.05208333334</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B7">
-        <v>5490</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46107.0625</v>
+        <v>46111.0625</v>
       </c>
       <c r="B8">
-        <v>5480</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46107.07291666666</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B9">
-        <v>5470</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46107.08333333334</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B10">
-        <v>5470</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46107.09375</v>
+        <v>46111.09375</v>
       </c>
       <c r="B11">
-        <v>5470</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46107.10416666666</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B12">
-        <v>5470</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46107.11458333334</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B13">
-        <v>5480</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46107.125</v>
+        <v>46111.125</v>
       </c>
       <c r="B14">
-        <v>5490</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46107.13541666666</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B15">
-        <v>5510</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46107.14583333334</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B16">
-        <v>5530</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46107.15625</v>
+        <v>46111.15625</v>
       </c>
       <c r="B17">
-        <v>5580</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46107.16666666666</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B18">
-        <v>5640</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46107.17708333334</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B19">
-        <v>5710</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46107.1875</v>
+        <v>46111.1875</v>
       </c>
       <c r="B20">
-        <v>5800</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46107.19791666666</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B21">
-        <v>5910</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46107.20833333334</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B22">
-        <v>6030</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46107.21875</v>
+        <v>46111.21875</v>
       </c>
       <c r="B23">
-        <v>6160</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46107.22916666666</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B24">
-        <v>6270</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46107.23958333334</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B25">
-        <v>6380</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46107.25</v>
+        <v>46111.25</v>
       </c>
       <c r="B26">
-        <v>6480</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46107.26041666666</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B27">
-        <v>6570</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46107.27083333334</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B28">
-        <v>6620</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46107.28125</v>
+        <v>46111.28125</v>
       </c>
       <c r="B29">
-        <v>6640</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46107.29166666666</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B30">
-        <v>6630</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46107.30208333334</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B31">
-        <v>6580</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46107.3125</v>
+        <v>46111.3125</v>
       </c>
       <c r="B32">
-        <v>6520</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46107.32291666666</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B33">
-        <v>6420</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46107.33333333334</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="B34">
-        <v>6320</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46107.34375</v>
+        <v>46111.34375</v>
       </c>
       <c r="B35">
-        <v>6180</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46107.35416666666</v>
+        <v>46111.35416666666</v>
       </c>
       <c r="B36">
-        <v>6060</v>
+        <v>7110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46107.36458333334</v>
+        <v>46111.36458333334</v>
       </c>
       <c r="B37">
-        <v>5940</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46107.375</v>
+        <v>46111.375</v>
       </c>
       <c r="B38">
-        <v>5810</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46107.38541666666</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="B39">
-        <v>5690</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46107.39583333334</v>
+        <v>46111.39583333334</v>
       </c>
       <c r="B40">
-        <v>5580</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46107.40625</v>
+        <v>46111.40625</v>
       </c>
       <c r="B41">
-        <v>5480</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46107.41666666666</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="B42">
-        <v>5390</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46107.42708333334</v>
+        <v>46111.42708333334</v>
       </c>
       <c r="B43">
-        <v>5320</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46107.4375</v>
+        <v>46111.4375</v>
       </c>
       <c r="B44">
-        <v>5260</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46107.44791666666</v>
+        <v>46111.44791666666</v>
       </c>
       <c r="B45">
-        <v>5210</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46107.45833333334</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="B46">
-        <v>5170</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46107.46875</v>
+        <v>46111.46875</v>
       </c>
       <c r="B47">
-        <v>5150</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46107.47916666666</v>
+        <v>46111.47916666666</v>
       </c>
       <c r="B48">
-        <v>5140</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46107.48958333334</v>
+        <v>46111.48958333334</v>
       </c>
       <c r="B49">
-        <v>5140</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46107.5</v>
+        <v>46111.5</v>
       </c>
       <c r="B50">
-        <v>5160</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46107.51041666666</v>
+        <v>46111.51041666666</v>
       </c>
       <c r="B51">
-        <v>5190</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46107.52083333334</v>
+        <v>46111.52083333334</v>
       </c>
       <c r="B52">
-        <v>5240</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46107.53125</v>
+        <v>46111.53125</v>
       </c>
       <c r="B53">
-        <v>5300</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46107.54166666666</v>
+        <v>46111.54166666666</v>
       </c>
       <c r="B54">
-        <v>5370</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46107.55208333334</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="B55">
-        <v>5450</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46107.5625</v>
+        <v>46111.5625</v>
       </c>
       <c r="B56">
-        <v>5530</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46107.57291666666</v>
+        <v>46111.57291666666</v>
       </c>
       <c r="B57">
-        <v>5610</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46107.58333333334</v>
+        <v>46111.58333333334</v>
       </c>
       <c r="B58">
-        <v>5700</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46107.59375</v>
+        <v>46111.59375</v>
       </c>
       <c r="B59">
-        <v>5790</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46107.60416666666</v>
+        <v>46111.60416666666</v>
       </c>
       <c r="B60">
-        <v>5890</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46107.61458333334</v>
+        <v>46111.61458333334</v>
       </c>
       <c r="B61">
-        <v>5990</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46107.625</v>
+        <v>46111.625</v>
       </c>
       <c r="B62">
-        <v>6100</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46107.63541666666</v>
+        <v>46111.63541666666</v>
       </c>
       <c r="B63">
-        <v>6220</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46107.64583333334</v>
+        <v>46111.64583333334</v>
       </c>
       <c r="B64">
-        <v>6350</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46107.65625</v>
+        <v>46111.65625</v>
       </c>
       <c r="B65">
-        <v>6470</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46107.66666666666</v>
+        <v>46111.66666666666</v>
       </c>
       <c r="B66">
         <v>6580</v>
@@ -914,215 +914,215 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46107.67708333334</v>
+        <v>46111.67708333334</v>
       </c>
       <c r="B67">
-        <v>6720</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46107.6875</v>
+        <v>46111.6875</v>
       </c>
       <c r="B68">
-        <v>6830</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46107.69791666666</v>
+        <v>46111.69791666666</v>
       </c>
       <c r="B69">
-        <v>6940</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46107.70833333334</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="B70">
-        <v>7040</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46107.71875</v>
+        <v>46111.71875</v>
       </c>
       <c r="B71">
-        <v>7160</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46107.72916666666</v>
+        <v>46111.72916666666</v>
       </c>
       <c r="B72">
-        <v>7290</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46107.73958333334</v>
+        <v>46111.73958333334</v>
       </c>
       <c r="B73">
-        <v>7420</v>
+        <v>7110</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46107.75</v>
+        <v>46111.75</v>
       </c>
       <c r="B74">
-        <v>7550</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46107.76041666666</v>
+        <v>46111.76041666666</v>
       </c>
       <c r="B75">
-        <v>7660</v>
+        <v>7310</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46107.77083333334</v>
+        <v>46111.77083333334</v>
       </c>
       <c r="B76">
-        <v>7720</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46107.78125</v>
+        <v>46111.78125</v>
       </c>
       <c r="B77">
-        <v>7740</v>
+        <v>7520</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46107.79166666666</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B78">
-        <v>7710</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46107.80208333334</v>
+        <v>46111.80208333334</v>
       </c>
       <c r="B79">
-        <v>7670</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46107.8125</v>
+        <v>46111.8125</v>
       </c>
       <c r="B80">
-        <v>7590</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46107.82291666666</v>
+        <v>46111.82291666666</v>
       </c>
       <c r="B81">
-        <v>7510</v>
+        <v>7610</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46107.83333333334</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B82">
-        <v>7400</v>
+        <v>7520</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46107.84375</v>
+        <v>46111.84375</v>
       </c>
       <c r="B83">
-        <v>7290</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46107.85416666666</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B84">
-        <v>7180</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46107.86458333334</v>
+        <v>46111.86458333334</v>
       </c>
       <c r="B85">
-        <v>7050</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46107.875</v>
+        <v>46111.875</v>
       </c>
       <c r="B86">
-        <v>6900</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46107.88541666666</v>
+        <v>46111.88541666666</v>
       </c>
       <c r="B87">
-        <v>6760</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46107.89583333334</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B88">
-        <v>6600</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46107.90625</v>
+        <v>46111.90625</v>
       </c>
       <c r="B89">
-        <v>6440</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46107.91666666666</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B90">
-        <v>6290</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46107.92708333334</v>
+        <v>46111.92708333334</v>
       </c>
       <c r="B91">
-        <v>6150</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46107.9375</v>
+        <v>46111.9375</v>
       </c>
       <c r="B92">
-        <v>6020</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46107.94791666666</v>
+        <v>46111.94791666666</v>
       </c>
       <c r="B93">
         <v>5900</v>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46107.95833333334</v>
+        <v>46111.95833333334</v>
       </c>
       <c r="B94">
-        <v>5880</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46107.96875</v>
+        <v>46111.96875</v>
       </c>
       <c r="B95">
         <v>5820</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46107.97916666666</v>
+        <v>46111.97916666666</v>
       </c>
       <c r="B96">
         <v>5770</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46107.98958333334</v>
+        <v>46111.98958333334</v>
       </c>
       <c r="B97">
-        <v>5720</v>
+        <v>5730</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,719 +394,719 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="B2">
-        <v>4960</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46111.01041666666</v>
+        <v>46115.01041666666</v>
       </c>
       <c r="B3">
-        <v>4960</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46111.02083333334</v>
+        <v>46115.02083333334</v>
       </c>
       <c r="B4">
-        <v>4960</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46111.03125</v>
+        <v>46115.03125</v>
       </c>
       <c r="B5">
-        <v>4960</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46111.04166666666</v>
+        <v>46115.04166666666</v>
       </c>
       <c r="B6">
-        <v>4960</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46111.05208333334</v>
+        <v>46115.05208333334</v>
       </c>
       <c r="B7">
-        <v>4940</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46111.0625</v>
+        <v>46115.0625</v>
       </c>
       <c r="B8">
-        <v>4930</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46111.07291666666</v>
+        <v>46115.07291666666</v>
       </c>
       <c r="B9">
-        <v>4930</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46111.08333333334</v>
+        <v>46115.08333333334</v>
       </c>
       <c r="B10">
-        <v>4920</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46111.09375</v>
+        <v>46115.09375</v>
       </c>
       <c r="B11">
-        <v>4920</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46111.10416666666</v>
+        <v>46115.10416666666</v>
       </c>
       <c r="B12">
-        <v>4930</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46111.11458333334</v>
+        <v>46115.11458333334</v>
       </c>
       <c r="B13">
-        <v>4940</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46111.125</v>
+        <v>46115.125</v>
       </c>
       <c r="B14">
-        <v>4960</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46111.13541666666</v>
+        <v>46115.13541666666</v>
       </c>
       <c r="B15">
-        <v>4980</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46111.14583333334</v>
+        <v>46115.14583333334</v>
       </c>
       <c r="B16">
-        <v>5000</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46111.15625</v>
+        <v>46115.15625</v>
       </c>
       <c r="B17">
-        <v>5060</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46111.16666666666</v>
+        <v>46115.16666666666</v>
       </c>
       <c r="B18">
-        <v>5130</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46111.17708333334</v>
+        <v>46115.17708333334</v>
       </c>
       <c r="B19">
-        <v>5210</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46111.1875</v>
+        <v>46115.1875</v>
       </c>
       <c r="B20">
-        <v>5330</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46111.19791666666</v>
+        <v>46115.19791666666</v>
       </c>
       <c r="B21">
-        <v>5470</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46111.20833333334</v>
+        <v>46115.20833333334</v>
       </c>
       <c r="B22">
-        <v>5620</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46111.21875</v>
+        <v>46115.21875</v>
       </c>
       <c r="B23">
-        <v>5790</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46111.22916666666</v>
+        <v>46115.22916666666</v>
       </c>
       <c r="B24">
-        <v>5970</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46111.23958333334</v>
+        <v>46115.23958333334</v>
       </c>
       <c r="B25">
-        <v>6150</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46111.25</v>
+        <v>46115.25</v>
       </c>
       <c r="B26">
-        <v>6320</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46111.26041666666</v>
+        <v>46115.26041666666</v>
       </c>
       <c r="B27">
-        <v>6490</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46111.27083333334</v>
+        <v>46115.27083333334</v>
       </c>
       <c r="B28">
-        <v>6640</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46111.28125</v>
+        <v>46115.28125</v>
       </c>
       <c r="B29">
-        <v>6780</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46111.29166666666</v>
+        <v>46115.29166666666</v>
       </c>
       <c r="B30">
-        <v>6890</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46111.30208333334</v>
+        <v>46115.30208333334</v>
       </c>
       <c r="B31">
-        <v>6980</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46111.3125</v>
+        <v>46115.3125</v>
       </c>
       <c r="B32">
-        <v>7050</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46111.32291666666</v>
+        <v>46115.32291666666</v>
       </c>
       <c r="B33">
-        <v>7100</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46111.33333333334</v>
+        <v>46115.33333333334</v>
       </c>
       <c r="B34">
-        <v>7130</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46111.34375</v>
+        <v>46115.34375</v>
       </c>
       <c r="B35">
-        <v>7130</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46111.35416666666</v>
+        <v>46115.35416666666</v>
       </c>
       <c r="B36">
-        <v>7110</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46111.36458333334</v>
+        <v>46115.36458333334</v>
       </c>
       <c r="B37">
-        <v>7080</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46111.375</v>
+        <v>46115.375</v>
       </c>
       <c r="B38">
-        <v>7030</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46111.38541666666</v>
+        <v>46115.38541666666</v>
       </c>
       <c r="B39">
-        <v>6970</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46111.39583333334</v>
+        <v>46115.39583333334</v>
       </c>
       <c r="B40">
-        <v>6910</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46111.40625</v>
+        <v>46115.40625</v>
       </c>
       <c r="B41">
-        <v>6840</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46111.41666666666</v>
+        <v>46115.41666666666</v>
       </c>
       <c r="B42">
-        <v>6770</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46111.42708333334</v>
+        <v>46115.42708333334</v>
       </c>
       <c r="B43">
-        <v>6700</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46111.4375</v>
+        <v>46115.4375</v>
       </c>
       <c r="B44">
-        <v>6630</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46111.44791666666</v>
+        <v>46115.44791666666</v>
       </c>
       <c r="B45">
-        <v>6570</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46111.45833333334</v>
+        <v>46115.45833333334</v>
       </c>
       <c r="B46">
-        <v>6510</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46111.46875</v>
+        <v>46115.46875</v>
       </c>
       <c r="B47">
-        <v>6460</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46111.47916666666</v>
+        <v>46115.47916666666</v>
       </c>
       <c r="B48">
-        <v>6410</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46111.48958333334</v>
+        <v>46115.48958333334</v>
       </c>
       <c r="B49">
-        <v>6380</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46111.5</v>
+        <v>46115.5</v>
       </c>
       <c r="B50">
-        <v>6350</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46111.51041666666</v>
+        <v>46115.51041666666</v>
       </c>
       <c r="B51">
-        <v>6320</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46111.52083333334</v>
+        <v>46115.52083333334</v>
       </c>
       <c r="B52">
-        <v>6310</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46111.53125</v>
+        <v>46115.53125</v>
       </c>
       <c r="B53">
-        <v>6300</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46111.54166666666</v>
+        <v>46115.54166666666</v>
       </c>
       <c r="B54">
-        <v>6310</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46111.55208333334</v>
+        <v>46115.55208333334</v>
       </c>
       <c r="B55">
-        <v>6310</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46111.5625</v>
+        <v>46115.5625</v>
       </c>
       <c r="B56">
-        <v>6320</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46111.57291666666</v>
+        <v>46115.57291666666</v>
       </c>
       <c r="B57">
-        <v>6320</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46111.58333333334</v>
+        <v>46115.58333333334</v>
       </c>
       <c r="B58">
-        <v>6330</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46111.59375</v>
+        <v>46115.59375</v>
       </c>
       <c r="B59">
-        <v>6340</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46111.60416666666</v>
+        <v>46115.60416666666</v>
       </c>
       <c r="B60">
-        <v>6350</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46111.61458333334</v>
+        <v>46115.61458333334</v>
       </c>
       <c r="B61">
-        <v>6370</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46111.625</v>
+        <v>46115.625</v>
       </c>
       <c r="B62">
-        <v>6390</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46111.63541666666</v>
+        <v>46115.63541666666</v>
       </c>
       <c r="B63">
-        <v>6430</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46111.64583333334</v>
+        <v>46115.64583333334</v>
       </c>
       <c r="B64">
-        <v>6480</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46111.65625</v>
+        <v>46115.65625</v>
       </c>
       <c r="B65">
-        <v>6530</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46111.66666666666</v>
+        <v>46115.66666666666</v>
       </c>
       <c r="B66">
-        <v>6580</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46111.67708333334</v>
+        <v>46115.67708333334</v>
       </c>
       <c r="B67">
-        <v>6640</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46111.6875</v>
+        <v>46115.6875</v>
       </c>
       <c r="B68">
-        <v>6720</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46111.69791666666</v>
+        <v>46115.69791666666</v>
       </c>
       <c r="B69">
-        <v>6780</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46111.70833333334</v>
+        <v>46115.70833333334</v>
       </c>
       <c r="B70">
-        <v>6860</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46111.71875</v>
+        <v>46115.71875</v>
       </c>
       <c r="B71">
-        <v>6950</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46111.72916666666</v>
+        <v>46115.72916666666</v>
       </c>
       <c r="B72">
-        <v>7020</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46111.73958333334</v>
+        <v>46115.73958333334</v>
       </c>
       <c r="B73">
-        <v>7110</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46111.75</v>
+        <v>46115.75</v>
       </c>
       <c r="B74">
-        <v>7210</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46111.76041666666</v>
+        <v>46115.76041666666</v>
       </c>
       <c r="B75">
-        <v>7310</v>
+        <v>7110</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46111.77083333334</v>
+        <v>46115.77083333334</v>
       </c>
       <c r="B76">
-        <v>7410</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46111.78125</v>
+        <v>46115.78125</v>
       </c>
       <c r="B77">
-        <v>7520</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46111.79166666666</v>
+        <v>46115.79166666666</v>
       </c>
       <c r="B78">
-        <v>7600</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46111.80208333334</v>
+        <v>46115.80208333334</v>
       </c>
       <c r="B79">
-        <v>7640</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46111.8125</v>
+        <v>46115.8125</v>
       </c>
       <c r="B80">
-        <v>7640</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46111.82291666666</v>
+        <v>46115.82291666666</v>
       </c>
       <c r="B81">
-        <v>7610</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46111.83333333334</v>
+        <v>46115.83333333334</v>
       </c>
       <c r="B82">
-        <v>7520</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46111.84375</v>
+        <v>46115.84375</v>
       </c>
       <c r="B83">
-        <v>7400</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46111.85416666666</v>
+        <v>46115.85416666666</v>
       </c>
       <c r="B84">
-        <v>7280</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46111.86458333334</v>
+        <v>46115.86458333334</v>
       </c>
       <c r="B85">
-        <v>7150</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46111.875</v>
+        <v>46115.875</v>
       </c>
       <c r="B86">
-        <v>7010</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46111.88541666666</v>
+        <v>46115.88541666666</v>
       </c>
       <c r="B87">
-        <v>6840</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46111.89583333334</v>
+        <v>46115.89583333334</v>
       </c>
       <c r="B88">
-        <v>6680</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46111.90625</v>
+        <v>46115.90625</v>
       </c>
       <c r="B89">
-        <v>6500</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46111.91666666666</v>
+        <v>46115.91666666666</v>
       </c>
       <c r="B90">
-        <v>6340</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46111.92708333334</v>
+        <v>46115.92708333334</v>
       </c>
       <c r="B91">
         <v>6180</v>
@@ -1114,23 +1114,23 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46111.9375</v>
+        <v>46115.9375</v>
       </c>
       <c r="B92">
-        <v>6050</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46111.94791666666</v>
+        <v>46115.94791666666</v>
       </c>
       <c r="B93">
-        <v>5900</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46111.95833333334</v>
+        <v>46115.95833333334</v>
       </c>
       <c r="B94">
         <v>5850</v>
@@ -1138,26 +1138,26 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46111.96875</v>
+        <v>46115.96875</v>
       </c>
       <c r="B95">
-        <v>5820</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46111.97916666666</v>
+        <v>46115.97916666666</v>
       </c>
       <c r="B96">
-        <v>5770</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46111.98958333334</v>
+        <v>46115.98958333334</v>
       </c>
       <c r="B97">
-        <v>5730</v>
+        <v>5670</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>5440</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46115.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>5440</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46115.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>5440</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46115.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>5440</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46115.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>5440</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46115.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>5440</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46115.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>5440</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46115.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>5440</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46115.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>5420</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46115.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>5410</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46115.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>5390</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46115.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>5380</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46115.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>5370</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46115.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>5370</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46115.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>5370</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46115.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>5380</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46115.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>5480</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46115.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>5580</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46115.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>5700</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46115.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>5820</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46115.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>5960</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46115.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>6100</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46115.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>6220</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46115.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>6370</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46115.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>6550</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46115.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>6700</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46115.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>6830</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46115.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>6960</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46115.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>7100</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46115.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>7190</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46115.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>7270</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46115.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>7320</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46115.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>7330</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46115.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>7320</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46115.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>7300</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46115.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>7250</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46115.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>7190</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46115.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>7100</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46115.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>7030</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46115.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>6960</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46115.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>6850</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46115.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>6780</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46115.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>6720</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46115.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>6660</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46115.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>6600</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46115.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>6540</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46115.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>6490</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46115.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>6450</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46115.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>6400</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46115.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>6370</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46115.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>6350</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46115.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>6320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46115.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>6280</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46115.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>6270</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46115.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>6270</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46115.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>6260</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46115.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>6220</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46115.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>6220</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46115.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>6220</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46115.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>6220</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46115.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>6260</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46115.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>6290</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46115.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>6310</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46115.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>6320</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46115.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>6340</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46115.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>6380</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46115.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>6420</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46115.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>6480</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46115.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>6610</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46115.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>6720</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46115.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>6810</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46115.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>6910</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46115.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>7010</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46115.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>7110</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46115.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>7200</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46115.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>7300</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46115.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>7380</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46115.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>7440</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46115.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>7450</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46115.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>7450</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46115.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>7370</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46115.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>7280</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46115.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>7190</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46115.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>7070</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46115.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>6910</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46115.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>6780</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46115.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>6610</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46115.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>6450</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46115.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>6320</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46115.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>6180</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46115.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>6060</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46115.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>5950</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46115.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>5850</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46115.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>5800</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46115.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>5750</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46115.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>5670</v>
+        <v>5290</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,719 +394,719 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B2">
-        <v>5100</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B3">
-        <v>5100</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B4">
-        <v>5100</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B5">
-        <v>5100</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B6">
-        <v>5100</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B8">
-        <v>5080</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B9">
-        <v>5070</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B10">
-        <v>5070</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B11">
-        <v>5070</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B12">
-        <v>5070</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B13">
-        <v>5080</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B14">
-        <v>5100</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B15">
-        <v>5110</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B16">
-        <v>5130</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B17">
-        <v>5150</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B18">
-        <v>5190</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B19">
-        <v>5250</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B20">
-        <v>5300</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B21">
-        <v>5370</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B22">
-        <v>5450</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B23">
-        <v>5540</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B24">
-        <v>5630</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B25">
-        <v>5720</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B26">
-        <v>5870</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B27">
-        <v>5950</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B28">
-        <v>5990</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B29">
-        <v>5990</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B30">
-        <v>5970</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B31">
-        <v>5920</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B32">
-        <v>5860</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B33">
-        <v>5770</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B34">
-        <v>5660</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46129.34375</v>
+        <v>46132.34375</v>
       </c>
       <c r="B35">
-        <v>5530</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46129.35416666666</v>
+        <v>46132.35416666666</v>
       </c>
       <c r="B36">
-        <v>5400</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46129.36458333334</v>
+        <v>46132.36458333334</v>
       </c>
       <c r="B37">
-        <v>5250</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46129.375</v>
+        <v>46132.375</v>
       </c>
       <c r="B38">
-        <v>5090</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46129.38541666666</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="B39">
-        <v>4950</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46129.39583333334</v>
+        <v>46132.39583333334</v>
       </c>
       <c r="B40">
-        <v>4830</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46129.40625</v>
+        <v>46132.40625</v>
       </c>
       <c r="B41">
-        <v>4730</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46129.41666666666</v>
+        <v>46132.41666666666</v>
       </c>
       <c r="B42">
-        <v>4640</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46129.42708333334</v>
+        <v>46132.42708333334</v>
       </c>
       <c r="B43">
-        <v>4570</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46129.4375</v>
+        <v>46132.4375</v>
       </c>
       <c r="B44">
-        <v>4520</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46129.44791666666</v>
+        <v>46132.44791666666</v>
       </c>
       <c r="B45">
-        <v>4470</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46129.45833333334</v>
+        <v>46132.45833333334</v>
       </c>
       <c r="B46">
-        <v>4430</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46129.46875</v>
+        <v>46132.46875</v>
       </c>
       <c r="B47">
-        <v>4400</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46129.47916666666</v>
+        <v>46132.47916666666</v>
       </c>
       <c r="B48">
-        <v>4390</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.48958333334</v>
       </c>
       <c r="B49">
-        <v>4390</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46129.5</v>
+        <v>46132.5</v>
       </c>
       <c r="B50">
-        <v>4400</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46129.51041666666</v>
+        <v>46132.51041666666</v>
       </c>
       <c r="B51">
-        <v>4400</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46129.52083333334</v>
+        <v>46132.52083333334</v>
       </c>
       <c r="B52">
-        <v>4400</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46129.53125</v>
+        <v>46132.53125</v>
       </c>
       <c r="B53">
-        <v>4400</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46129.54166666666</v>
+        <v>46132.54166666666</v>
       </c>
       <c r="B54">
-        <v>4410</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46129.55208333334</v>
+        <v>46132.55208333334</v>
       </c>
       <c r="B55">
-        <v>4420</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46129.5625</v>
+        <v>46132.5625</v>
       </c>
       <c r="B56">
-        <v>4420</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46129.57291666666</v>
+        <v>46132.57291666666</v>
       </c>
       <c r="B57">
-        <v>4430</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46129.58333333334</v>
+        <v>46132.58333333334</v>
       </c>
       <c r="B58">
-        <v>4500</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46129.59375</v>
+        <v>46132.59375</v>
       </c>
       <c r="B59">
-        <v>4570</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46129.60416666666</v>
+        <v>46132.60416666666</v>
       </c>
       <c r="B60">
-        <v>4620</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46129.61458333334</v>
+        <v>46132.61458333334</v>
       </c>
       <c r="B61">
-        <v>4690</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46129.625</v>
+        <v>46132.625</v>
       </c>
       <c r="B62">
-        <v>4770</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46129.63541666666</v>
+        <v>46132.63541666666</v>
       </c>
       <c r="B63">
-        <v>4860</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46129.64583333334</v>
+        <v>46132.64583333334</v>
       </c>
       <c r="B64">
-        <v>4940</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46129.65625</v>
+        <v>46132.65625</v>
       </c>
       <c r="B65">
-        <v>5040</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46129.66666666666</v>
+        <v>46132.66666666666</v>
       </c>
       <c r="B66">
-        <v>5150</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46129.67708333334</v>
+        <v>46132.67708333334</v>
       </c>
       <c r="B67">
-        <v>5250</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46129.6875</v>
+        <v>46132.6875</v>
       </c>
       <c r="B68">
-        <v>5350</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46129.69791666666</v>
+        <v>46132.69791666666</v>
       </c>
       <c r="B69">
-        <v>5460</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46129.70833333334</v>
+        <v>46132.70833333334</v>
       </c>
       <c r="B70">
-        <v>5570</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46129.71875</v>
+        <v>46132.71875</v>
       </c>
       <c r="B71">
-        <v>5680</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46129.72916666666</v>
+        <v>46132.72916666666</v>
       </c>
       <c r="B72">
-        <v>5810</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46129.73958333334</v>
+        <v>46132.73958333334</v>
       </c>
       <c r="B73">
-        <v>5960</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46129.75</v>
+        <v>46132.75</v>
       </c>
       <c r="B74">
-        <v>6110</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46129.76041666666</v>
+        <v>46132.76041666666</v>
       </c>
       <c r="B75">
-        <v>6280</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46129.77083333334</v>
+        <v>46132.77083333334</v>
       </c>
       <c r="B76">
-        <v>6440</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46129.78125</v>
+        <v>46132.78125</v>
       </c>
       <c r="B77">
-        <v>6580</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46129.79166666666</v>
+        <v>46132.79166666666</v>
       </c>
       <c r="B78">
-        <v>6730</v>
+        <v>6990</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46129.80208333334</v>
+        <v>46132.80208333334</v>
       </c>
       <c r="B79">
-        <v>6850</v>
+        <v>7060</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46129.8125</v>
+        <v>46132.8125</v>
       </c>
       <c r="B80">
-        <v>6920</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46129.82291666666</v>
+        <v>46132.82291666666</v>
       </c>
       <c r="B81">
-        <v>6940</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46129.83333333334</v>
+        <v>46132.83333333334</v>
       </c>
       <c r="B82">
-        <v>6920</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46129.84375</v>
+        <v>46132.84375</v>
       </c>
       <c r="B83">
-        <v>6860</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46129.85416666666</v>
+        <v>46132.85416666666</v>
       </c>
       <c r="B84">
-        <v>6800</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46129.86458333334</v>
+        <v>46132.86458333334</v>
       </c>
       <c r="B85">
-        <v>6690</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46129.875</v>
+        <v>46132.875</v>
       </c>
       <c r="B86">
-        <v>6540</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46129.88541666666</v>
+        <v>46132.88541666666</v>
       </c>
       <c r="B87">
-        <v>6400</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46129.89583333334</v>
+        <v>46132.89583333334</v>
       </c>
       <c r="B88">
-        <v>6240</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46129.90625</v>
+        <v>46132.90625</v>
       </c>
       <c r="B89">
-        <v>6100</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46129.91666666666</v>
+        <v>46132.91666666666</v>
       </c>
       <c r="B90">
-        <v>5970</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46129.92708333334</v>
+        <v>46132.92708333334</v>
       </c>
       <c r="B91">
         <v>5820</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46129.9375</v>
+        <v>46132.9375</v>
       </c>
       <c r="B92">
         <v>5710</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46129.94791666666</v>
+        <v>46132.94791666666</v>
       </c>
       <c r="B93">
         <v>5600</v>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46129.95833333334</v>
+        <v>46132.95833333334</v>
       </c>
       <c r="B94">
-        <v>5470</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46129.96875</v>
+        <v>46132.96875</v>
       </c>
       <c r="B95">
-        <v>5430</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46129.97916666666</v>
+        <v>46132.97916666666</v>
       </c>
       <c r="B96">
-        <v>5370</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46129.98958333334</v>
+        <v>46132.98958333334</v>
       </c>
       <c r="B97">
-        <v>5290</v>
+        <v>5310</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>4560</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>4560</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>4560</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>4560</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>4560</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>4560</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>4560</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>4560</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>4550</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>4550</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>4550</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>4560</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>4590</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>4610</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>4640</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>4680</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>4720</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>4790</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>4890</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>5010</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>5160</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>5300</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>5440</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>5580</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>5770</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>5900</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>5980</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>6030</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>6080</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>6080</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>6070</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>6040</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>5990</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>5930</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>5850</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>5760</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>5690</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>5600</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>5530</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>5460</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>5360</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>5310</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>5270</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>5260</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>5250</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>5250</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>5250</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>5250</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>5250</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>5260</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>5260</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>5260</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>5270</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>5290</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>5310</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>5330</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>5370</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>5400</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>5430</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>5480</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>5520</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>5580</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>5650</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>5720</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>5800</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>5880</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>5960</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>6040</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>6160</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>6250</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>6340</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>6450</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>6550</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>6670</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>6780</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>6880</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>6990</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>7060</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>7100</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>7130</v>
+        <v>7230</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>7090</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>7020</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>6920</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>6810</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>6620</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>6470</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>6310</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>6160</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>5980</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>5820</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>5710</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>5480</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>5440</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>5380</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>5310</v>
+        <v>5460</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,719 +394,719 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B2">
-        <v>5100</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46139.01041666666</v>
       </c>
       <c r="B3">
-        <v>5100</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46139.02083333334</v>
       </c>
       <c r="B4">
-        <v>5100</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46139.03125</v>
       </c>
       <c r="B5">
-        <v>5100</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46139.04166666666</v>
       </c>
       <c r="B6">
-        <v>5100</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46139.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46139.0625</v>
       </c>
       <c r="B8">
-        <v>5070</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46139.07291666666</v>
       </c>
       <c r="B9">
-        <v>5060</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46139.08333333334</v>
       </c>
       <c r="B10">
-        <v>5060</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46139.09375</v>
       </c>
       <c r="B11">
-        <v>5060</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46139.10416666666</v>
       </c>
       <c r="B12">
-        <v>5060</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46139.11458333334</v>
       </c>
       <c r="B13">
-        <v>5060</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46139.125</v>
       </c>
       <c r="B14">
-        <v>5070</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46139.13541666666</v>
       </c>
       <c r="B15">
-        <v>5080</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46139.14583333334</v>
       </c>
       <c r="B16">
-        <v>5100</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46139.15625</v>
       </c>
       <c r="B17">
-        <v>5130</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46139.16666666666</v>
       </c>
       <c r="B18">
-        <v>5180</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46139.17708333334</v>
       </c>
       <c r="B19">
-        <v>5240</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46139.1875</v>
       </c>
       <c r="B20">
-        <v>5330</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46139.19791666666</v>
       </c>
       <c r="B21">
-        <v>5440</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46139.20833333334</v>
       </c>
       <c r="B22">
-        <v>5560</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46139.21875</v>
       </c>
       <c r="B23">
-        <v>5680</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46139.22916666666</v>
       </c>
       <c r="B24">
-        <v>5810</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46139.23958333334</v>
       </c>
       <c r="B25">
-        <v>5930</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46139.25</v>
       </c>
       <c r="B26">
-        <v>6040</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46139.26041666666</v>
       </c>
       <c r="B27">
-        <v>6150</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46139.27083333334</v>
       </c>
       <c r="B28">
-        <v>6240</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46139.28125</v>
       </c>
       <c r="B29">
-        <v>6310</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46139.29166666666</v>
       </c>
       <c r="B30">
-        <v>6370</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46139.30208333334</v>
       </c>
       <c r="B31">
-        <v>6400</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46139.3125</v>
       </c>
       <c r="B32">
-        <v>6410</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46139.32291666666</v>
       </c>
       <c r="B33">
-        <v>6390</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46139.33333333334</v>
       </c>
       <c r="B34">
-        <v>6350</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46139.34375</v>
       </c>
       <c r="B35">
-        <v>6290</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="B36">
-        <v>6210</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46139.36458333334</v>
       </c>
       <c r="B37">
-        <v>6110</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46139.375</v>
       </c>
       <c r="B38">
-        <v>6010</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="B39">
-        <v>5910</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46139.39583333334</v>
       </c>
       <c r="B40">
-        <v>5810</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46139.40625</v>
       </c>
       <c r="B41">
-        <v>5720</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46139.41666666666</v>
       </c>
       <c r="B42">
-        <v>5650</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46139.42708333334</v>
       </c>
       <c r="B43">
-        <v>5590</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46139.4375</v>
       </c>
       <c r="B44">
-        <v>5550</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46139.44791666666</v>
       </c>
       <c r="B45">
-        <v>5520</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46139.45833333334</v>
       </c>
       <c r="B46">
-        <v>5500</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46139.46875</v>
       </c>
       <c r="B47">
-        <v>5490</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46139.47916666666</v>
       </c>
       <c r="B48">
-        <v>5480</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46139.48958333334</v>
       </c>
       <c r="B49">
-        <v>5480</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46139.5</v>
       </c>
       <c r="B50">
-        <v>5470</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46139.51041666666</v>
       </c>
       <c r="B51">
-        <v>5470</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46139.52083333334</v>
       </c>
       <c r="B52">
-        <v>5470</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46139.53125</v>
       </c>
       <c r="B53">
-        <v>5470</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46139.54166666666</v>
       </c>
       <c r="B54">
-        <v>5480</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46139.55208333334</v>
       </c>
       <c r="B55">
-        <v>5490</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46139.5625</v>
       </c>
       <c r="B56">
-        <v>5510</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46139.57291666666</v>
       </c>
       <c r="B57">
-        <v>5540</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46139.58333333334</v>
       </c>
       <c r="B58">
-        <v>5560</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46139.59375</v>
       </c>
       <c r="B59">
-        <v>5590</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46139.60416666666</v>
       </c>
       <c r="B60">
-        <v>5620</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46139.61458333334</v>
       </c>
       <c r="B61">
-        <v>5650</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46139.625</v>
       </c>
       <c r="B62">
-        <v>5700</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46139.63541666666</v>
       </c>
       <c r="B63">
-        <v>5750</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46139.64583333334</v>
       </c>
       <c r="B64">
-        <v>5820</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46139.65625</v>
       </c>
       <c r="B65">
-        <v>5880</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46139.66666666666</v>
       </c>
       <c r="B66">
-        <v>5960</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46139.67708333334</v>
       </c>
       <c r="B67">
-        <v>6050</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46139.6875</v>
       </c>
       <c r="B68">
-        <v>6130</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46139.69791666666</v>
       </c>
       <c r="B69">
-        <v>6220</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46139.70833333334</v>
       </c>
       <c r="B70">
-        <v>6300</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46139.71875</v>
       </c>
       <c r="B71">
-        <v>6410</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46139.72916666666</v>
       </c>
       <c r="B72">
-        <v>6490</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46139.73958333334</v>
       </c>
       <c r="B73">
-        <v>6590</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46139.75</v>
       </c>
       <c r="B74">
-        <v>6700</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46139.76041666666</v>
       </c>
       <c r="B75">
-        <v>6810</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46139.77083333334</v>
       </c>
       <c r="B76">
-        <v>6920</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46139.78125</v>
       </c>
       <c r="B77">
-        <v>7000</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46139.79166666666</v>
       </c>
       <c r="B78">
-        <v>7090</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46139.80208333334</v>
       </c>
       <c r="B79">
-        <v>7170</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46139.8125</v>
       </c>
       <c r="B80">
-        <v>7200</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46139.82291666666</v>
       </c>
       <c r="B81">
-        <v>7230</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46139.83333333334</v>
       </c>
       <c r="B82">
-        <v>7190</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46139.84375</v>
       </c>
       <c r="B83">
-        <v>7130</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46139.85416666666</v>
       </c>
       <c r="B84">
-        <v>7040</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46139.86458333334</v>
       </c>
       <c r="B85">
-        <v>6930</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46139.875</v>
       </c>
       <c r="B86">
-        <v>6770</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46139.88541666666</v>
       </c>
       <c r="B87">
-        <v>6620</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46139.89583333334</v>
       </c>
       <c r="B88">
-        <v>6460</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46139.90625</v>
       </c>
       <c r="B89">
-        <v>6280</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46139.91666666666</v>
       </c>
       <c r="B90">
-        <v>6120</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46139.92708333334</v>
       </c>
       <c r="B91">
         <v>5950</v>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46139.9375</v>
       </c>
       <c r="B92">
-        <v>5820</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46139.94791666666</v>
       </c>
       <c r="B93">
         <v>5700</v>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46139.95833333334</v>
       </c>
       <c r="B94">
-        <v>5620</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46139.96875</v>
       </c>
       <c r="B95">
-        <v>5570</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46139.97916666666</v>
       </c>
       <c r="B96">
-        <v>5510</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46139.98958333334</v>
       </c>
       <c r="B97">
-        <v>5460</v>
+        <v>5260</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B2">
-        <v>4650</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
-        <v>4650</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
-        <v>4650</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>4650</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
-        <v>4650</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
-        <v>4640</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
-        <v>4630</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
-        <v>4620</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
-        <v>4610</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
-        <v>4600</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
-        <v>4610</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
-        <v>4620</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
-        <v>4630</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
-        <v>4650</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
-        <v>4670</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
-        <v>4700</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>4760</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
-        <v>4830</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>4920</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>5020</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>5130</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>5250</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>5370</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>5490</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>5610</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>5710</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>5790</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>5850</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>5880</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>5880</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>5850</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>5780</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>5690</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>5570</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>5420</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
-        <v>5270</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>5120</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>4960</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>4830</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
-        <v>4710</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>4610</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>4540</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>4490</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>4460</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>4450</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>4440</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>4440</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>4450</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46139.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B50">
-        <v>4460</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46139.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B51">
-        <v>4470</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46139.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B52">
-        <v>4480</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46139.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B53">
-        <v>4480</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46139.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B54">
-        <v>4490</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46139.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B55">
-        <v>4500</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46139.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B56">
-        <v>4510</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46139.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B57">
-        <v>4530</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46139.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B58">
-        <v>4540</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46139.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B59">
-        <v>4560</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46139.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B60">
-        <v>4590</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46139.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B61">
-        <v>4630</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46139.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B62">
-        <v>4690</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46139.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B63">
-        <v>4770</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46139.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B64">
-        <v>4870</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46139.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B65">
-        <v>4990</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46139.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B66">
-        <v>5120</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46139.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B67">
-        <v>5260</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46139.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B68">
-        <v>5380</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46139.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B69">
-        <v>5530</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46139.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B70">
-        <v>5660</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46139.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B71">
-        <v>5800</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46139.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B72">
-        <v>5940</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46139.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B73">
-        <v>6090</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46139.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B74">
-        <v>6240</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46139.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B75">
-        <v>6400</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46139.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B76">
-        <v>6550</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46139.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B77">
-        <v>6710</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46139.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B78">
-        <v>6840</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46139.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B79">
-        <v>6940</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46139.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B80">
-        <v>7010</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46139.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B81">
-        <v>7050</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46139.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B82">
-        <v>7030</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46139.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B83">
-        <v>7000</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46139.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B84">
-        <v>6920</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46139.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B85">
-        <v>6800</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46139.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B86">
-        <v>6670</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46139.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B87">
-        <v>6550</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46139.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B88">
-        <v>6410</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46139.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B89">
-        <v>6250</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46139.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B90">
-        <v>6090</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46139.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B91">
-        <v>5950</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46139.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B92">
-        <v>5810</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46139.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B93">
-        <v>5700</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46139.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B94">
-        <v>5500</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46139.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B95">
-        <v>5410</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46139.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B96">
-        <v>5330</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46139.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B97">
-        <v>5260</v>
+        <v>5510</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B2">
-        <v>5290</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B3">
-        <v>5290</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B4">
-        <v>5290</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B5">
-        <v>5290</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B6">
-        <v>5290</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B7">
-        <v>5280</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B8">
-        <v>5270</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B9">
-        <v>5260</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B10">
-        <v>5250</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B11">
-        <v>5240</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B12">
-        <v>5240</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B13">
-        <v>5250</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B14">
-        <v>5260</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B15">
-        <v>5270</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B16">
-        <v>5280</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B17">
-        <v>5310</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B18">
-        <v>5370</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B19">
-        <v>5430</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B20">
-        <v>5510</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B21">
-        <v>5600</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B22">
-        <v>5700</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B23">
-        <v>5810</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B24">
-        <v>5910</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B25">
-        <v>6030</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B26">
-        <v>6190</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B27">
-        <v>6340</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B28">
-        <v>6460</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B29">
-        <v>6550</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B30">
-        <v>6600</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B31">
-        <v>6630</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B32">
-        <v>6660</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B33">
-        <v>6670</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B34">
-        <v>6660</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B35">
-        <v>6630</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B36">
-        <v>6580</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B37">
-        <v>6530</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B38">
-        <v>6470</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46142.38541666666</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="B39">
-        <v>6400</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46142.39583333334</v>
+        <v>46146.39583333334</v>
       </c>
       <c r="B40">
-        <v>6330</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46142.40625</v>
+        <v>46146.40625</v>
       </c>
       <c r="B41">
-        <v>6260</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46142.41666666666</v>
+        <v>46146.41666666666</v>
       </c>
       <c r="B42">
-        <v>6180</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46142.42708333334</v>
+        <v>46146.42708333334</v>
       </c>
       <c r="B43">
-        <v>6110</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46142.4375</v>
+        <v>46146.4375</v>
       </c>
       <c r="B44">
-        <v>6050</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46142.44791666666</v>
+        <v>46146.44791666666</v>
       </c>
       <c r="B45">
-        <v>6000</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46142.45833333334</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="B46">
-        <v>5930</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46142.46875</v>
+        <v>46146.46875</v>
       </c>
       <c r="B47">
-        <v>5890</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46142.47916666666</v>
+        <v>46146.47916666666</v>
       </c>
       <c r="B48">
-        <v>5860</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46142.48958333334</v>
+        <v>46146.48958333334</v>
       </c>
       <c r="B49">
-        <v>5820</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46142.5</v>
+        <v>46146.5</v>
       </c>
       <c r="B50">
-        <v>5810</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46142.51041666666</v>
+        <v>46146.51041666666</v>
       </c>
       <c r="B51">
-        <v>5780</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46142.52083333334</v>
+        <v>46146.52083333334</v>
       </c>
       <c r="B52">
-        <v>5770</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46142.53125</v>
+        <v>46146.53125</v>
       </c>
       <c r="B53">
-        <v>5760</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46142.54166666666</v>
+        <v>46146.54166666666</v>
       </c>
       <c r="B54">
-        <v>5740</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46142.55208333334</v>
+        <v>46146.55208333334</v>
       </c>
       <c r="B55">
-        <v>5730</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46142.5625</v>
+        <v>46146.5625</v>
       </c>
       <c r="B56">
-        <v>5720</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46142.57291666666</v>
+        <v>46146.57291666666</v>
       </c>
       <c r="B57">
-        <v>5710</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46142.58333333334</v>
+        <v>46146.58333333334</v>
       </c>
       <c r="B58">
-        <v>5700</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46142.59375</v>
+        <v>46146.59375</v>
       </c>
       <c r="B59">
-        <v>5700</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46142.60416666666</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B60">
-        <v>5710</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46142.61458333334</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="B61">
-        <v>5720</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46142.625</v>
+        <v>46146.625</v>
       </c>
       <c r="B62">
-        <v>5740</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46142.63541666666</v>
+        <v>46146.63541666666</v>
       </c>
       <c r="B63">
-        <v>5790</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46142.64583333334</v>
+        <v>46146.64583333334</v>
       </c>
       <c r="B64">
-        <v>5840</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46142.65625</v>
+        <v>46146.65625</v>
       </c>
       <c r="B65">
-        <v>5900</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46142.66666666666</v>
+        <v>46146.66666666666</v>
       </c>
       <c r="B66">
-        <v>5970</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46142.67708333334</v>
+        <v>46146.67708333334</v>
       </c>
       <c r="B67">
-        <v>6040</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46142.6875</v>
+        <v>46146.6875</v>
       </c>
       <c r="B68">
-        <v>6120</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46142.69791666666</v>
+        <v>46146.69791666666</v>
       </c>
       <c r="B69">
-        <v>6210</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46142.70833333334</v>
+        <v>46146.70833333334</v>
       </c>
       <c r="B70">
-        <v>6320</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46142.71875</v>
+        <v>46146.71875</v>
       </c>
       <c r="B71">
-        <v>6420</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46142.72916666666</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="B72">
-        <v>6520</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46142.73958333334</v>
+        <v>46146.73958333334</v>
       </c>
       <c r="B73">
-        <v>6610</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46142.75</v>
+        <v>46146.75</v>
       </c>
       <c r="B74">
-        <v>6720</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46142.76041666666</v>
+        <v>46146.76041666666</v>
       </c>
       <c r="B75">
-        <v>6830</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46142.77083333334</v>
+        <v>46146.77083333334</v>
       </c>
       <c r="B76">
-        <v>6940</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46142.78125</v>
+        <v>46146.78125</v>
       </c>
       <c r="B77">
-        <v>7030</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46142.79166666666</v>
+        <v>46146.79166666666</v>
       </c>
       <c r="B78">
-        <v>7160</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46142.80208333334</v>
+        <v>46146.80208333334</v>
       </c>
       <c r="B79">
-        <v>7250</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46142.8125</v>
+        <v>46146.8125</v>
       </c>
       <c r="B80">
-        <v>7280</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46142.82291666666</v>
+        <v>46146.82291666666</v>
       </c>
       <c r="B81">
-        <v>7300</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46142.83333333334</v>
+        <v>46146.83333333334</v>
       </c>
       <c r="B82">
-        <v>7270</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46142.84375</v>
+        <v>46146.84375</v>
       </c>
       <c r="B83">
-        <v>7210</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46142.85416666666</v>
+        <v>46146.85416666666</v>
       </c>
       <c r="B84">
-        <v>7120</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46142.86458333334</v>
+        <v>46146.86458333334</v>
       </c>
       <c r="B85">
-        <v>7000</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46142.875</v>
+        <v>46146.875</v>
       </c>
       <c r="B86">
-        <v>6830</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46142.88541666666</v>
+        <v>46146.88541666666</v>
       </c>
       <c r="B87">
-        <v>6670</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46142.89583333334</v>
+        <v>46146.89583333334</v>
       </c>
       <c r="B88">
-        <v>6530</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46142.90625</v>
+        <v>46146.90625</v>
       </c>
       <c r="B89">
-        <v>6370</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46142.91666666666</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="B90">
-        <v>6220</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46142.92708333334</v>
+        <v>46146.92708333334</v>
       </c>
       <c r="B91">
-        <v>6090</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46142.9375</v>
+        <v>46146.9375</v>
       </c>
       <c r="B92">
-        <v>5970</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46142.94791666666</v>
+        <v>46146.94791666666</v>
       </c>
       <c r="B93">
-        <v>5850</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46142.95833333334</v>
+        <v>46146.95833333334</v>
       </c>
       <c r="B94">
-        <v>5660</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46142.96875</v>
+        <v>46146.96875</v>
       </c>
       <c r="B95">
-        <v>5610</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46142.97916666666</v>
+        <v>46146.97916666666</v>
       </c>
       <c r="B96">
-        <v>5560</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46142.98958333334</v>
+        <v>46146.98958333334</v>
       </c>
       <c r="B97">
-        <v>5510</v>
+        <v>5420</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,247 +394,247 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B2">
-        <v>4670</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B3">
-        <v>4670</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B4">
-        <v>4670</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B5">
-        <v>4670</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B6">
-        <v>4670</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B7">
-        <v>4650</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B8">
-        <v>4640</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B9">
-        <v>4640</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B10">
-        <v>4640</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B11">
-        <v>4640</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B12">
-        <v>4640</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B13">
-        <v>4650</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B14">
-        <v>4660</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B15">
-        <v>4680</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B16">
-        <v>4700</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B17">
-        <v>4730</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B18">
-        <v>4780</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B19">
-        <v>4840</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B20">
-        <v>4930</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B21">
-        <v>5050</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B22">
-        <v>5180</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B23">
-        <v>5320</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B24">
-        <v>5450</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B25">
-        <v>5590</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B26">
-        <v>5730</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B27">
-        <v>5810</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B28">
-        <v>5810</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B29">
-        <v>5780</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B30">
-        <v>5740</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B31">
-        <v>5700</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B32">
         <v>5630</v>
@@ -642,391 +642,391 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B33">
-        <v>5500</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46146.33333333334</v>
+        <v>46148.33333333334</v>
       </c>
       <c r="B34">
-        <v>5320</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46146.34375</v>
+        <v>46148.34375</v>
       </c>
       <c r="B35">
-        <v>5140</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.35416666666</v>
       </c>
       <c r="B36">
-        <v>4960</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46146.36458333334</v>
+        <v>46148.36458333334</v>
       </c>
       <c r="B37">
-        <v>4780</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46146.375</v>
+        <v>46148.375</v>
       </c>
       <c r="B38">
-        <v>4620</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46146.38541666666</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="B39">
-        <v>4460</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46146.39583333334</v>
+        <v>46148.39583333334</v>
       </c>
       <c r="B40">
-        <v>4320</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46146.40625</v>
+        <v>46148.40625</v>
       </c>
       <c r="B41">
-        <v>4200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46146.41666666666</v>
+        <v>46148.41666666666</v>
       </c>
       <c r="B42">
-        <v>4080</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46146.42708333334</v>
+        <v>46148.42708333334</v>
       </c>
       <c r="B43">
-        <v>3980</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46146.4375</v>
+        <v>46148.4375</v>
       </c>
       <c r="B44">
-        <v>3930</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46146.44791666666</v>
+        <v>46148.44791666666</v>
       </c>
       <c r="B45">
-        <v>3890</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46146.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="B46">
-        <v>3880</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46146.46875</v>
+        <v>46148.46875</v>
       </c>
       <c r="B47">
-        <v>3880</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46146.47916666666</v>
+        <v>46148.47916666666</v>
       </c>
       <c r="B48">
-        <v>3880</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46146.48958333334</v>
+        <v>46148.48958333334</v>
       </c>
       <c r="B49">
-        <v>3870</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46146.5</v>
+        <v>46148.5</v>
       </c>
       <c r="B50">
-        <v>3860</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46146.51041666666</v>
+        <v>46148.51041666666</v>
       </c>
       <c r="B51">
-        <v>3850</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46146.52083333334</v>
+        <v>46148.52083333334</v>
       </c>
       <c r="B52">
-        <v>3850</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46146.53125</v>
+        <v>46148.53125</v>
       </c>
       <c r="B53">
-        <v>3850</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46146.54166666666</v>
+        <v>46148.54166666666</v>
       </c>
       <c r="B54">
-        <v>3870</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46146.55208333334</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="B55">
-        <v>3870</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46146.5625</v>
+        <v>46148.5625</v>
       </c>
       <c r="B56">
-        <v>3880</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46146.57291666666</v>
+        <v>46148.57291666666</v>
       </c>
       <c r="B57">
-        <v>3900</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46146.58333333334</v>
+        <v>46148.58333333334</v>
       </c>
       <c r="B58">
-        <v>3950</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46146.59375</v>
+        <v>46148.59375</v>
       </c>
       <c r="B59">
-        <v>3990</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46146.60416666666</v>
+        <v>46148.60416666666</v>
       </c>
       <c r="B60">
-        <v>4040</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46146.61458333334</v>
+        <v>46148.61458333334</v>
       </c>
       <c r="B61">
-        <v>4100</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46146.625</v>
+        <v>46148.625</v>
       </c>
       <c r="B62">
-        <v>4160</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46146.63541666666</v>
+        <v>46148.63541666666</v>
       </c>
       <c r="B63">
-        <v>4240</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46146.64583333334</v>
+        <v>46148.64583333334</v>
       </c>
       <c r="B64">
-        <v>4340</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46146.65625</v>
+        <v>46148.65625</v>
       </c>
       <c r="B65">
-        <v>4460</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46146.66666666666</v>
+        <v>46148.66666666666</v>
       </c>
       <c r="B66">
-        <v>4610</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46146.67708333334</v>
+        <v>46148.67708333334</v>
       </c>
       <c r="B67">
-        <v>4770</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46146.6875</v>
+        <v>46148.6875</v>
       </c>
       <c r="B68">
-        <v>4930</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46146.69791666666</v>
+        <v>46148.69791666666</v>
       </c>
       <c r="B69">
-        <v>5090</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46146.70833333334</v>
+        <v>46148.70833333334</v>
       </c>
       <c r="B70">
-        <v>5290</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46146.71875</v>
+        <v>46148.71875</v>
       </c>
       <c r="B71">
-        <v>5460</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46146.72916666666</v>
+        <v>46148.72916666666</v>
       </c>
       <c r="B72">
-        <v>5630</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46146.73958333334</v>
+        <v>46148.73958333334</v>
       </c>
       <c r="B73">
-        <v>5820</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46146.75</v>
+        <v>46148.75</v>
       </c>
       <c r="B74">
-        <v>6020</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46146.76041666666</v>
+        <v>46148.76041666666</v>
       </c>
       <c r="B75">
-        <v>6210</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46146.77083333334</v>
+        <v>46148.77083333334</v>
       </c>
       <c r="B76">
-        <v>6380</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46146.78125</v>
+        <v>46148.78125</v>
       </c>
       <c r="B77">
-        <v>6510</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46146.79166666666</v>
+        <v>46148.79166666666</v>
       </c>
       <c r="B78">
-        <v>6620</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46146.80208333334</v>
+        <v>46148.80208333334</v>
       </c>
       <c r="B79">
-        <v>6710</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46146.8125</v>
+        <v>46148.8125</v>
       </c>
       <c r="B80">
-        <v>6790</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46146.82291666666</v>
+        <v>46148.82291666666</v>
       </c>
       <c r="B81">
         <v>6880</v>
@@ -1034,95 +1034,95 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46146.83333333334</v>
+        <v>46148.83333333334</v>
       </c>
       <c r="B82">
-        <v>6920</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46146.84375</v>
+        <v>46148.84375</v>
       </c>
       <c r="B83">
-        <v>6920</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46146.85416666666</v>
+        <v>46148.85416666666</v>
       </c>
       <c r="B84">
-        <v>6910</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46146.86458333334</v>
+        <v>46148.86458333334</v>
       </c>
       <c r="B85">
-        <v>6850</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46146.875</v>
+        <v>46148.875</v>
       </c>
       <c r="B86">
-        <v>6720</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46146.88541666666</v>
+        <v>46148.88541666666</v>
       </c>
       <c r="B87">
-        <v>6550</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46146.89583333334</v>
+        <v>46148.89583333334</v>
       </c>
       <c r="B88">
-        <v>6370</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46146.90625</v>
+        <v>46148.90625</v>
       </c>
       <c r="B89">
-        <v>6200</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46146.91666666666</v>
+        <v>46148.91666666666</v>
       </c>
       <c r="B90">
-        <v>6010</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46146.92708333334</v>
+        <v>46148.92708333334</v>
       </c>
       <c r="B91">
-        <v>5860</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46146.9375</v>
+        <v>46148.9375</v>
       </c>
       <c r="B92">
-        <v>5720</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46146.94791666666</v>
+        <v>46148.94791666666</v>
       </c>
       <c r="B93">
         <v>5640</v>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46146.95833333334</v>
+        <v>46148.95833333334</v>
       </c>
       <c r="B94">
-        <v>5630</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46146.96875</v>
+        <v>46148.96875</v>
       </c>
       <c r="B95">
-        <v>5550</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46146.97916666666</v>
+        <v>46148.97916666666</v>
       </c>
       <c r="B96">
-        <v>5490</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46146.98958333334</v>
+        <v>46148.98958333334</v>
       </c>
       <c r="B97">
-        <v>5420</v>
+        <v>5220</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,135 +394,135 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B2">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B3">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B4">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B5">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B6">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B7">
-        <v>5050</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B8">
-        <v>5020</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B9">
-        <v>5010</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B10">
-        <v>5010</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B11">
-        <v>5010</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B12">
-        <v>5020</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B13">
-        <v>5030</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B14">
-        <v>5050</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B15">
-        <v>5070</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B16">
-        <v>5080</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B17">
-        <v>5100</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B18">
         <v>5140</v>
@@ -530,47 +530,47 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B19">
-        <v>5190</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B20">
-        <v>5260</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B21">
-        <v>5340</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B22">
-        <v>5430</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B23">
-        <v>5520</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B24">
         <v>5610</v>
@@ -578,559 +578,559 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B25">
-        <v>5690</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B26">
-        <v>5760</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B27">
-        <v>5800</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B28">
-        <v>5820</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B29">
-        <v>5820</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B30">
-        <v>5780</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B31">
-        <v>5720</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B32">
-        <v>5630</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B33">
-        <v>5520</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B34">
-        <v>5390</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B35">
-        <v>5240</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B36">
-        <v>5090</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B37">
-        <v>4940</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B38">
-        <v>4790</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B39">
-        <v>4640</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B40">
-        <v>4510</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B41">
-        <v>4400</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B42">
-        <v>4300</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B43">
-        <v>4220</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B44">
-        <v>4160</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B45">
-        <v>4110</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B46">
-        <v>4070</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B47">
-        <v>4050</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B48">
-        <v>4030</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B49">
-        <v>4020</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B50">
-        <v>4020</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B51">
-        <v>4030</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B52">
-        <v>4040</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B53">
-        <v>4050</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B54">
-        <v>4060</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B55">
-        <v>4080</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B56">
-        <v>4100</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B57">
-        <v>4130</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B58">
-        <v>4160</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B59">
-        <v>4200</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B60">
-        <v>4260</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B61">
-        <v>4320</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B62">
-        <v>4410</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B63">
-        <v>4510</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B64">
-        <v>4620</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B65">
-        <v>4750</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B66">
-        <v>4900</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B67">
-        <v>5040</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B68">
-        <v>5170</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B69">
-        <v>5320</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B70">
-        <v>5460</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B71">
-        <v>5600</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B72">
-        <v>5760</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B73">
-        <v>5920</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B74">
-        <v>6080</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B75">
-        <v>6220</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B76">
-        <v>6370</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B77">
-        <v>6500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B78">
-        <v>6640</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B79">
-        <v>6770</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B80">
-        <v>6840</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B81">
-        <v>6880</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B82">
-        <v>6910</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B83">
-        <v>6890</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B84">
-        <v>6840</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B85">
-        <v>6770</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B86">
-        <v>6660</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B87">
-        <v>6540</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B88">
-        <v>6380</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B89">
-        <v>6220</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B90">
-        <v>6050</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B91">
-        <v>5900</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B92">
-        <v>5750</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B93">
-        <v>5640</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B94">
         <v>5380</v>
@@ -1138,26 +1138,26 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B95">
-        <v>5330</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B96">
-        <v>5280</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B97">
-        <v>5220</v>
+        <v>5210</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,591 +394,591 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>5090</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46150.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>5090</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46150.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>5090</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46150.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>5090</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46150.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>5090</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46150.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46150.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>5080</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46150.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>5070</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46150.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>5050</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46150.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>5050</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46150.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>5050</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46150.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>5060</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46150.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>5090</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46150.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>5090</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46150.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>5100</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46150.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>5120</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46150.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>5140</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46150.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>5180</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46150.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>5240</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46150.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>5320</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46150.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>5410</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46150.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>5510</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46150.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>5610</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46150.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>5710</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46150.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>5870</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46150.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>5960</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46150.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>6020</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46150.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>6060</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46150.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>6060</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46150.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>6040</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46150.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>6020</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46150.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>5970</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46150.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>5880</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46150.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>5780</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46150.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>5670</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46150.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>5550</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46150.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>5430</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46150.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>5320</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46150.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>5210</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46150.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>5110</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46150.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>4990</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46150.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>4920</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46150.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>4870</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46150.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>4830</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46150.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>4790</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46150.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>4770</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46150.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>4760</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46150.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>4760</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46150.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>4760</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46150.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>4770</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46150.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>4770</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46150.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>4780</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46150.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>4790</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46150.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>4800</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46150.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>4800</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46150.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>4820</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46150.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>4850</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46150.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>4880</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46150.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>4910</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46150.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>4970</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46150.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>5030</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46150.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>5100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46150.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>5180</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46150.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>5300</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46150.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>5420</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46150.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>5540</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46150.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>5660</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46150.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>5780</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46150.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>5900</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46150.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>6000</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46150.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>6100</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46150.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>6200</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46150.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>6300</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46150.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
         <v>6410</v>
@@ -986,23 +986,23 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46150.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>6500</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46150.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>6600</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46150.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
         <v>6700</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46150.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
         <v>6780</v>
@@ -1018,23 +1018,23 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46150.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>6830</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46150.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>6890</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46150.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
         <v>6930</v>
@@ -1042,79 +1042,79 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46150.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>6910</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46150.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>6830</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46150.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>6730</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46150.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>6570</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46150.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>6410</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46150.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>6260</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46150.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>6110</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46150.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>5950</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46150.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>5800</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46150.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
         <v>5700</v>
@@ -1122,42 +1122,42 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46150.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>5590</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46150.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>5380</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46150.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>5320</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46150.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>5260</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46150.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>5210</v>
+        <v>5570</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,687 +394,687 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>4600</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>4600</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>4600</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>4600</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>4600</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>4600</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>4600</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>4600</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>4600</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>4610</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>4620</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>4630</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>4640</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>4650</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>4670</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>4700</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>4740</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>4790</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>4870</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>4980</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>5100</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>5220</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>5330</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>5470</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>5630</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>5770</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>5820</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>5830</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>5820</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>5800</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>5760</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>5680</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>5560</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>5440</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>5320</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>5200</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>5090</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>4980</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>4880</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>4790</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>4690</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>4620</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>4570</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>4530</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>4490</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>4470</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>4460</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>4460</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>4480</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>4500</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>4520</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>4540</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>4560</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>4570</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>4580</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>4600</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>4620</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>4650</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>4700</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>4770</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>4890</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>5000</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>5130</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>5240</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>5370</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>5480</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>5580</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>5690</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>5800</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>5920</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>6020</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>6140</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>6280</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>6410</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>6520</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>6620</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>6700</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>6780</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>6850</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>6910</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>6930</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>6920</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>6890</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>6800</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>6660</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
         <v>6500</v>
@@ -1082,82 +1082,82 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>6330</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>6130</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>5960</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>5820</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>5700</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>5570</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>5570</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>5570</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>5570</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>5570</v>
+        <v>5270</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,103 +394,103 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B2">
-        <v>5090</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B3">
-        <v>5090</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B4">
-        <v>5090</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B5">
-        <v>5090</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B6">
-        <v>5090</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B8">
-        <v>5080</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B9">
-        <v>5080</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B10">
-        <v>5070</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B11">
-        <v>5070</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B12">
-        <v>5070</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B13">
-        <v>5080</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B14">
         <v>5100</v>
@@ -498,666 +498,666 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B15">
-        <v>5100</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B16">
-        <v>5100</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B17">
-        <v>5100</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B18">
-        <v>5110</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B19">
-        <v>5140</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B20">
-        <v>5180</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B21">
-        <v>5250</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B22">
-        <v>5310</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B23">
-        <v>5410</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B24">
-        <v>5510</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B25">
-        <v>5620</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B26">
-        <v>5820</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B27">
-        <v>5950</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B28">
-        <v>6030</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B29">
-        <v>6080</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B30">
-        <v>6110</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B31">
-        <v>6100</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B32">
-        <v>6100</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B33">
-        <v>6090</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B34">
-        <v>6060</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B35">
-        <v>6020</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B36">
-        <v>5990</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B37">
-        <v>5910</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B38">
-        <v>5830</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B39">
-        <v>5740</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B40">
-        <v>5650</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B41">
-        <v>5570</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B42">
-        <v>5460</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B43">
-        <v>5400</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B44">
-        <v>5350</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B45">
-        <v>5310</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B46">
-        <v>5280</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B47">
-        <v>5260</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B48">
-        <v>5240</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B49">
-        <v>5240</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B50">
-        <v>5240</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B51">
-        <v>5240</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B52">
-        <v>5240</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B53">
-        <v>5230</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B54">
-        <v>5210</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B55">
-        <v>5200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B56">
-        <v>5200</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B57">
-        <v>5210</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B58">
-        <v>5240</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B59">
-        <v>5260</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B60">
-        <v>5280</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B61">
-        <v>5310</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B62">
-        <v>5370</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B63">
-        <v>5430</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B64">
-        <v>5500</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B65">
-        <v>5570</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B66">
-        <v>5660</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B67">
-        <v>5740</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B68">
-        <v>5810</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B69">
-        <v>5900</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B70">
-        <v>6010</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B71">
-        <v>6100</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B72">
-        <v>6190</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B73">
-        <v>6300</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B74">
-        <v>6390</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B75">
-        <v>6510</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B76">
-        <v>6610</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B77">
-        <v>6690</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B78">
-        <v>6780</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B79">
-        <v>6860</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B80">
-        <v>6910</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B81">
-        <v>6970</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B82">
-        <v>7010</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B83">
-        <v>6980</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B84">
-        <v>6920</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B85">
-        <v>6810</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B86">
-        <v>6650</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B87">
-        <v>6500</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B88">
-        <v>6350</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B89">
-        <v>6190</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B90">
-        <v>6020</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B91">
-        <v>5860</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B92">
-        <v>5750</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B93">
-        <v>5640</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B94">
-        <v>5440</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B95">
-        <v>5410</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B96">
-        <v>5330</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B97">
-        <v>5270</v>
+        <v>5300</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>5110</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>5110</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>5110</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>5110</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>5110</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>5100</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>5100</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>5090</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>5080</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>5080</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>5080</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>5090</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>5100</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>5110</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>5120</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>5140</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>5160</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>5200</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>5250</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>5320</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>5380</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>5470</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>5540</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>5630</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>5790</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>5830</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>5840</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>5810</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>5740</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>5660</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>5580</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>5480</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>5320</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>5180</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>5030</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>4900</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>4780</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>4650</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>4530</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>4420</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>4270</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>4170</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>4130</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>4110</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>4090</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>4080</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>4080</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>4070</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>4070</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>4080</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>4080</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>4080</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>4080</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>4100</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>4100</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>4120</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>4180</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>4220</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>4270</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>4330</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>4400</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>4490</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>4600</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>4710</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>4830</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>4960</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>5100</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>5240</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>5430</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>5580</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>5740</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>5890</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>6040</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>6180</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>6280</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>6380</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>6460</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>6540</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>6620</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>6700</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>6760</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>6760</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>6750</v>
+        <v>6560</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>6690</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>6520</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>6400</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>6250</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>6110</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>5950</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>5810</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>5700</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>5590</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>5480</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>5440</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
-        <v>5380</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>5300</v>
+        <v>5220</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>4970</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>4970</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
-        <v>4970</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>4970</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>4970</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>4960</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>4950</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>4950</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>4950</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>4950</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>4960</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>4960</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>4960</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>4960</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>4960</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>4960</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>4970</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>4990</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>5020</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>5060</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>5110</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>5180</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>5260</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>5340</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>5420</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>5500</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>5560</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>5610</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>5640</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>5640</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>5630</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>5590</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>5530</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>5460</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>5370</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>5290</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>5210</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>5130</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>5060</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>5000</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>4950</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>4910</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>4880</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>4850</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>4830</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>4810</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>4790</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>4780</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>4770</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>4760</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>4760</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>4760</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>4770</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>4780</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>4790</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>4800</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>4810</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>4820</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>4840</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>4870</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>4900</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>4960</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>5020</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>5110</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>5200</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>5290</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>5380</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>5470</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>5560</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>5660</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>5780</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>5900</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>6000</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>6120</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>6220</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>6310</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>6390</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>6480</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>6540</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>6600</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>6620</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>6600</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>6560</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>6500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>6410</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>6300</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>6160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>6000</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>5850</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>5560</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>5460</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>5380</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>5350</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>5280</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>5220</v>
+        <v>5550</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B2">
-        <v>5030</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B3">
-        <v>5030</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B4">
-        <v>5030</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B5">
-        <v>5030</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B6">
-        <v>5030</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B7">
-        <v>5010</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B8">
-        <v>5000</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B9">
-        <v>5000</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B10">
-        <v>5000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B11">
-        <v>5000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B12">
-        <v>5010</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B13">
-        <v>5020</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B14">
-        <v>5030</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B15">
-        <v>5040</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B16">
-        <v>5050</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B17">
-        <v>5060</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B18">
-        <v>5080</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B19">
-        <v>5110</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B20">
-        <v>5150</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B21">
-        <v>5200</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B22">
-        <v>5270</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B23">
-        <v>5350</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B24">
-        <v>5440</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B25">
-        <v>5530</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B26">
-        <v>5630</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B27">
-        <v>5720</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B28">
-        <v>5800</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B29">
-        <v>5870</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B30">
-        <v>5920</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B31">
-        <v>5950</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B32">
-        <v>5950</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B33">
-        <v>5930</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B34">
-        <v>5890</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B35">
-        <v>5830</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B36">
-        <v>5760</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B37">
-        <v>5670</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B38">
-        <v>5590</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B39">
-        <v>5500</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B40">
-        <v>5410</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B41">
-        <v>5330</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B42">
-        <v>5260</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B43">
-        <v>5200</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B44">
-        <v>5150</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B45">
-        <v>5110</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B46">
-        <v>5080</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46164.46875</v>
+        <v>46167.46875</v>
       </c>
       <c r="B47">
-        <v>5050</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46164.47916666666</v>
+        <v>46167.47916666666</v>
       </c>
       <c r="B48">
-        <v>5030</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46164.48958333334</v>
+        <v>46167.48958333334</v>
       </c>
       <c r="B49">
-        <v>5020</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46164.5</v>
+        <v>46167.5</v>
       </c>
       <c r="B50">
-        <v>5020</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.51041666666</v>
       </c>
       <c r="B51">
-        <v>5020</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46164.52083333334</v>
+        <v>46167.52083333334</v>
       </c>
       <c r="B52">
-        <v>5020</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46164.53125</v>
+        <v>46167.53125</v>
       </c>
       <c r="B53">
-        <v>5030</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46164.54166666666</v>
+        <v>46167.54166666666</v>
       </c>
       <c r="B54">
-        <v>5040</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46164.55208333334</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="B55">
-        <v>5050</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46164.5625</v>
+        <v>46167.5625</v>
       </c>
       <c r="B56">
-        <v>5050</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46164.57291666666</v>
+        <v>46167.57291666666</v>
       </c>
       <c r="B57">
-        <v>5070</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46164.58333333334</v>
+        <v>46167.58333333334</v>
       </c>
       <c r="B58">
-        <v>5080</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46164.59375</v>
+        <v>46167.59375</v>
       </c>
       <c r="B59">
-        <v>5090</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46164.60416666666</v>
+        <v>46167.60416666666</v>
       </c>
       <c r="B60">
-        <v>5110</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46164.61458333334</v>
+        <v>46167.61458333334</v>
       </c>
       <c r="B61">
-        <v>5160</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46164.625</v>
+        <v>46167.625</v>
       </c>
       <c r="B62">
-        <v>5180</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46164.63541666666</v>
+        <v>46167.63541666666</v>
       </c>
       <c r="B63">
-        <v>5250</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46164.64583333334</v>
+        <v>46167.64583333334</v>
       </c>
       <c r="B64">
-        <v>5320</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46164.65625</v>
+        <v>46167.65625</v>
       </c>
       <c r="B65">
-        <v>5400</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46164.66666666666</v>
+        <v>46167.66666666666</v>
       </c>
       <c r="B66">
-        <v>5480</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46164.67708333334</v>
+        <v>46167.67708333334</v>
       </c>
       <c r="B67">
-        <v>5580</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46164.6875</v>
+        <v>46167.6875</v>
       </c>
       <c r="B68">
-        <v>5670</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46164.69791666666</v>
+        <v>46167.69791666666</v>
       </c>
       <c r="B69">
-        <v>5760</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46164.70833333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B70">
-        <v>5850</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46164.71875</v>
+        <v>46167.71875</v>
       </c>
       <c r="B71">
-        <v>5940</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46164.72916666666</v>
+        <v>46167.72916666666</v>
       </c>
       <c r="B72">
-        <v>6030</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46164.73958333334</v>
+        <v>46167.73958333334</v>
       </c>
       <c r="B73">
-        <v>6140</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46164.75</v>
+        <v>46167.75</v>
       </c>
       <c r="B74">
-        <v>6240</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46164.76041666666</v>
+        <v>46167.76041666666</v>
       </c>
       <c r="B75">
-        <v>6340</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46164.77083333334</v>
+        <v>46167.77083333334</v>
       </c>
       <c r="B76">
-        <v>6430</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46164.78125</v>
+        <v>46167.78125</v>
       </c>
       <c r="B77">
-        <v>6510</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46164.79166666666</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="B78">
-        <v>6570</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46164.80208333334</v>
+        <v>46167.80208333334</v>
       </c>
       <c r="B79">
-        <v>6640</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46164.8125</v>
+        <v>46167.8125</v>
       </c>
       <c r="B80">
-        <v>6690</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46164.82291666666</v>
+        <v>46167.82291666666</v>
       </c>
       <c r="B81">
-        <v>6720</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46164.83333333334</v>
+        <v>46167.83333333334</v>
       </c>
       <c r="B82">
-        <v>6730</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46164.84375</v>
+        <v>46167.84375</v>
       </c>
       <c r="B83">
-        <v>6700</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46164.85416666666</v>
+        <v>46167.85416666666</v>
       </c>
       <c r="B84">
-        <v>6670</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46164.86458333334</v>
+        <v>46167.86458333334</v>
       </c>
       <c r="B85">
-        <v>6600</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46164.875</v>
+        <v>46167.875</v>
       </c>
       <c r="B86">
-        <v>6500</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46164.88541666666</v>
+        <v>46167.88541666666</v>
       </c>
       <c r="B87">
-        <v>6380</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46164.89583333334</v>
+        <v>46167.89583333334</v>
       </c>
       <c r="B88">
-        <v>6240</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46164.90625</v>
+        <v>46167.90625</v>
       </c>
       <c r="B89">
-        <v>6080</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46164.91666666666</v>
+        <v>46167.91666666666</v>
       </c>
       <c r="B90">
-        <v>5940</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46164.92708333334</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B91">
-        <v>5800</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46164.9375</v>
+        <v>46167.9375</v>
       </c>
       <c r="B92">
-        <v>5660</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46164.94791666666</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="B93">
-        <v>5550</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46164.95833333334</v>
+        <v>46167.95833333334</v>
       </c>
       <c r="B94">
-        <v>5550</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46164.96875</v>
+        <v>46167.96875</v>
       </c>
       <c r="B95">
-        <v>5550</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46164.97916666666</v>
+        <v>46167.97916666666</v>
       </c>
       <c r="B96">
-        <v>5550</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46164.98958333334</v>
+        <v>46167.98958333334</v>
       </c>
       <c r="B97">
-        <v>5550</v>
+        <v>5120</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,351 +394,351 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>4430</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>4430</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>4430</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>4430</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>4430</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>4420</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>4410</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>4410</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>4400</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>4400</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>4410</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>4410</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>4420</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>4430</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>4440</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>4470</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>4510</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>4550</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>4620</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>4700</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>4780</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>4880</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>4970</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>5060</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>5140</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>5200</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>5240</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>5250</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>5230</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>5190</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>5130</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>5050</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>4950</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>4840</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>4740</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>4630</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>4530</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>4450</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>4380</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>4320</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>4280</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>4240</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>4220</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
         <v>4200</v>
@@ -746,199 +746,199 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>4180</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>4170</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>4160</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>4140</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>4140</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>4140</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>4140</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>4150</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>4170</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>4190</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>4220</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>4250</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>4280</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>4320</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>4370</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>4430</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>4500</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>4590</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>4700</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>4820</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>4940</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>5070</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>5190</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>5310</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
         <v>5430</v>
@@ -946,79 +946,79 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>5540</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>5660</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>5800</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>5920</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>6020</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>6120</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>6230</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>6330</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>6420</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
         <v>6500</v>
@@ -1026,135 +1026,135 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>6580</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>6650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>6670</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>6650</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>6580</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>6470</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>6340</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>6200</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>6050</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>5900</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>5750</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>5580</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>5450</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>5280</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>5220</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>5150</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
         <v>5120</v>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,687 +394,687 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46185</v>
       </c>
       <c r="B2">
-        <v>4870</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B3">
-        <v>4870</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B4">
-        <v>4870</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B5">
-        <v>4870</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B6">
-        <v>4870</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B7">
-        <v>4860</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B8">
-        <v>4860</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B9">
-        <v>4850</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B10">
-        <v>4830</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B11">
-        <v>4820</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B12">
-        <v>4820</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B13">
-        <v>4820</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B14">
-        <v>4830</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B15">
-        <v>4830</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B16">
-        <v>4830</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B17">
-        <v>4830</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B18">
-        <v>4830</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B19">
-        <v>4850</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B20">
-        <v>4890</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B21">
-        <v>4950</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B22">
-        <v>5000</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B23">
-        <v>5070</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B24">
-        <v>5120</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B25">
-        <v>5210</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B26">
-        <v>5340</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B27">
-        <v>5380</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B28">
-        <v>5400</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B29">
-        <v>5400</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B30">
-        <v>5350</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B31">
-        <v>5280</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B32">
-        <v>5210</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B33">
-        <v>5130</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B34">
-        <v>5010</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B35">
-        <v>4900</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B36">
-        <v>4780</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B37">
-        <v>4680</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B38">
-        <v>4590</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B39">
-        <v>4490</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B40">
-        <v>4410</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B41">
-        <v>4330</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B42">
-        <v>4240</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B43">
-        <v>4190</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B44">
-        <v>4190</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B45">
-        <v>4200</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B46">
-        <v>4200</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B47">
-        <v>4200</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B48">
-        <v>4200</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B49">
-        <v>4210</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B50">
-        <v>4250</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B51">
-        <v>4260</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B52">
-        <v>4270</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B53">
-        <v>4270</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B54">
-        <v>4270</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B55">
-        <v>4270</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B56">
-        <v>4280</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B57">
-        <v>4300</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B58">
-        <v>4350</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B59">
-        <v>4400</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B60">
-        <v>4430</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B61">
-        <v>4470</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B62">
-        <v>4520</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B63">
-        <v>4600</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B64">
-        <v>4680</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B65">
-        <v>4780</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B66">
-        <v>4880</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B67">
-        <v>5000</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B68">
-        <v>5120</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B69">
-        <v>5250</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B70">
-        <v>5430</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B71">
-        <v>5570</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B72">
-        <v>5720</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B73">
-        <v>5880</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B74">
-        <v>6010</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B75">
-        <v>6140</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B76">
-        <v>6230</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B77">
-        <v>6300</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B78">
-        <v>6350</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B79">
-        <v>6430</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B80">
-        <v>6500</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B81">
-        <v>6600</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B82">
-        <v>6700</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B83">
-        <v>6700</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B84">
-        <v>6700</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B85">
-        <v>6620</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B86">
-        <v>6460</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B87">
         <v>6330</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B88">
         <v>6190</v>
@@ -1090,74 +1090,74 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B89">
-        <v>6020</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B90">
-        <v>5840</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B91">
-        <v>5700</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B92">
-        <v>5590</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B93">
-        <v>5480</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B94">
-        <v>5310</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B95">
-        <v>5280</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B96">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B97">
-        <v>5120</v>
+        <v>5230</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>5060</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
-        <v>5010</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
-        <v>4960</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>4910</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
-        <v>4880</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
-        <v>4850</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>4830</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
-        <v>4820</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>4810</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>4800</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>4800</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>4810</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>4830</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>4840</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>4860</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>4880</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
-        <v>4900</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
-        <v>4930</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>4970</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>5020</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>5090</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>5150</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>5230</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>5340</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>5480</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>5580</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>5660</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>5720</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>5770</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>5810</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>5810</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>5780</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>5710</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>5600</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>5500</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>5400</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>5310</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>5230</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>5160</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>5080</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>4990</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>4940</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>4920</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>4920</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>4920</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46216.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
-        <v>4930</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46216.47916666666</v>
+        <v>46218.47916666666</v>
       </c>
       <c r="B48">
-        <v>4940</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46216.48958333334</v>
+        <v>46218.48958333334</v>
       </c>
       <c r="B49">
-        <v>4950</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46216.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>5000</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46216.51041666666</v>
+        <v>46218.51041666666</v>
       </c>
       <c r="B51">
-        <v>5050</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46216.52083333334</v>
+        <v>46218.52083333334</v>
       </c>
       <c r="B52">
-        <v>5100</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46216.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>5120</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46216.54166666666</v>
+        <v>46218.54166666666</v>
       </c>
       <c r="B54">
-        <v>5140</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46216.55208333334</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="B55">
-        <v>5160</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46216.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>5170</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46216.57291666666</v>
+        <v>46218.57291666666</v>
       </c>
       <c r="B57">
-        <v>5180</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46216.58333333334</v>
+        <v>46218.58333333334</v>
       </c>
       <c r="B58">
-        <v>5210</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46216.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>5230</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46216.60416666666</v>
+        <v>46218.60416666666</v>
       </c>
       <c r="B60">
-        <v>5250</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46216.61458333334</v>
+        <v>46218.61458333334</v>
       </c>
       <c r="B61">
-        <v>5290</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46216.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>5350</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46216.63541666666</v>
+        <v>46218.63541666666</v>
       </c>
       <c r="B63">
-        <v>5400</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46216.64583333334</v>
+        <v>46218.64583333334</v>
       </c>
       <c r="B64">
-        <v>5470</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46216.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>5560</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46216.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="B66">
-        <v>5650</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46216.67708333334</v>
+        <v>46218.67708333334</v>
       </c>
       <c r="B67">
-        <v>5730</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46216.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>5820</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46216.69791666666</v>
+        <v>46218.69791666666</v>
       </c>
       <c r="B69">
-        <v>5900</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46216.70833333334</v>
+        <v>46218.70833333334</v>
       </c>
       <c r="B70">
-        <v>6000</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46216.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
-        <v>6100</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46216.72916666666</v>
+        <v>46218.72916666666</v>
       </c>
       <c r="B72">
-        <v>6200</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46216.73958333334</v>
+        <v>46218.73958333334</v>
       </c>
       <c r="B73">
-        <v>6290</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46216.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>6380</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46216.76041666666</v>
+        <v>46218.76041666666</v>
       </c>
       <c r="B75">
-        <v>6470</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46216.77083333334</v>
+        <v>46218.77083333334</v>
       </c>
       <c r="B76">
-        <v>6540</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46216.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>6610</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46216.79166666666</v>
+        <v>46218.79166666666</v>
       </c>
       <c r="B78">
-        <v>6680</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46216.80208333334</v>
+        <v>46218.80208333334</v>
       </c>
       <c r="B79">
-        <v>6760</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46216.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
-        <v>6810</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46216.82291666666</v>
+        <v>46218.82291666666</v>
       </c>
       <c r="B81">
-        <v>6870</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46216.83333333334</v>
+        <v>46218.83333333334</v>
       </c>
       <c r="B82">
-        <v>6910</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46216.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
-        <v>6910</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46216.85416666666</v>
+        <v>46218.85416666666</v>
       </c>
       <c r="B84">
-        <v>6900</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46216.86458333334</v>
+        <v>46218.86458333334</v>
       </c>
       <c r="B85">
-        <v>6840</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46216.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>6740</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46216.88541666666</v>
+        <v>46218.88541666666</v>
       </c>
       <c r="B87">
-        <v>6580</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46216.89583333334</v>
+        <v>46218.89583333334</v>
       </c>
       <c r="B88">
-        <v>6420</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46216.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
-        <v>6270</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46216.91666666666</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="B90">
-        <v>6130</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46216.92708333334</v>
+        <v>46218.92708333334</v>
       </c>
       <c r="B91">
-        <v>6010</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46216.9375</v>
+        <v>46218.9375</v>
       </c>
       <c r="B92">
-        <v>5900</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46216.94791666666</v>
+        <v>46218.94791666666</v>
       </c>
       <c r="B93">
-        <v>5780</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46216.95833333334</v>
+        <v>46218.95833333334</v>
       </c>
       <c r="B94">
-        <v>5720</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46216.96875</v>
+        <v>46218.96875</v>
       </c>
       <c r="B95">
-        <v>5670</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46216.97916666666</v>
+        <v>46218.97916666666</v>
       </c>
       <c r="B96">
-        <v>5610</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46216.98958333334</v>
+        <v>46218.98958333334</v>
       </c>
       <c r="B97">
-        <v>5550</v>
+        <v>5750</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>5230</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
-        <v>5170</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
-        <v>5120</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46223.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>5090</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
-        <v>5040</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
-        <v>5000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46223.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>4990</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
-        <v>4980</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
-        <v>4960</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46223.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>4950</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
-        <v>4950</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
-        <v>4960</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46223.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>4970</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
-        <v>4980</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
-        <v>4980</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46223.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>4990</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
-        <v>5020</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
-        <v>5070</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46223.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>5120</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
-        <v>5170</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>5250</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46223.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>5350</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>5440</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>5560</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46223.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>5750</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>5870</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>5950</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46223.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>6030</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>6070</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>6070</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46223.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>6070</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46223.32291666666</v>
+        <v>46226.32291666666</v>
       </c>
       <c r="B33">
-        <v>6060</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46223.33333333334</v>
+        <v>46226.33333333334</v>
       </c>
       <c r="B34">
-        <v>6010</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46223.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>5960</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46223.35416666666</v>
+        <v>46226.35416666666</v>
       </c>
       <c r="B36">
-        <v>5890</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46223.36458333334</v>
+        <v>46226.36458333334</v>
       </c>
       <c r="B37">
-        <v>5820</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46223.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>5730</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46223.38541666666</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="B39">
-        <v>5660</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46223.39583333334</v>
+        <v>46226.39583333334</v>
       </c>
       <c r="B40">
-        <v>5610</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46223.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>5560</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46223.41666666666</v>
+        <v>46226.41666666666</v>
       </c>
       <c r="B42">
-        <v>5510</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46223.42708333334</v>
+        <v>46226.42708333334</v>
       </c>
       <c r="B43">
-        <v>5500</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46223.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
-        <v>5500</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46223.44791666666</v>
+        <v>46226.44791666666</v>
       </c>
       <c r="B45">
-        <v>5500</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46223.45833333334</v>
+        <v>46226.45833333334</v>
       </c>
       <c r="B46">
-        <v>5500</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46223.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>5500</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46223.47916666666</v>
+        <v>46226.47916666666</v>
       </c>
       <c r="B48">
-        <v>5500</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46223.48958333334</v>
+        <v>46226.48958333334</v>
       </c>
       <c r="B49">
-        <v>5510</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46223.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>5540</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46223.51041666666</v>
+        <v>46226.51041666666</v>
       </c>
       <c r="B51">
-        <v>5570</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46223.52083333334</v>
+        <v>46226.52083333334</v>
       </c>
       <c r="B52">
-        <v>5590</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46223.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>5620</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46223.54166666666</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="B54">
-        <v>5660</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46223.55208333334</v>
+        <v>46226.55208333334</v>
       </c>
       <c r="B55">
-        <v>5690</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46223.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>5710</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46223.57291666666</v>
+        <v>46226.57291666666</v>
       </c>
       <c r="B57">
-        <v>5750</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46223.58333333334</v>
+        <v>46226.58333333334</v>
       </c>
       <c r="B58">
-        <v>5810</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46223.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
-        <v>5850</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46223.60416666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="B60">
-        <v>5890</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46223.61458333334</v>
+        <v>46226.61458333334</v>
       </c>
       <c r="B61">
-        <v>5940</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46223.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
-        <v>6010</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46223.63541666666</v>
+        <v>46226.63541666666</v>
       </c>
       <c r="B63">
-        <v>6080</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46223.64583333334</v>
+        <v>46226.64583333334</v>
       </c>
       <c r="B64">
-        <v>6150</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46223.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>6230</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46223.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="B66">
-        <v>6300</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46223.67708333334</v>
+        <v>46226.67708333334</v>
       </c>
       <c r="B67">
-        <v>6390</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46223.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>6470</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46223.69791666666</v>
+        <v>46226.69791666666</v>
       </c>
       <c r="B69">
-        <v>6550</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46223.70833333334</v>
+        <v>46226.70833333334</v>
       </c>
       <c r="B70">
-        <v>6650</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46223.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>6740</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46223.72916666666</v>
+        <v>46226.72916666666</v>
       </c>
       <c r="B72">
-        <v>6800</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46223.73958333334</v>
+        <v>46226.73958333334</v>
       </c>
       <c r="B73">
-        <v>6870</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46223.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
-        <v>6930</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46223.76041666666</v>
+        <v>46226.76041666666</v>
       </c>
       <c r="B75">
-        <v>6990</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46223.77083333334</v>
+        <v>46226.77083333334</v>
       </c>
       <c r="B76">
-        <v>7030</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46223.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
-        <v>7060</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46223.79166666666</v>
+        <v>46226.79166666666</v>
       </c>
       <c r="B78">
-        <v>7090</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46223.80208333334</v>
+        <v>46226.80208333334</v>
       </c>
       <c r="B79">
-        <v>7130</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46223.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
-        <v>7160</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46223.82291666666</v>
+        <v>46226.82291666666</v>
       </c>
       <c r="B81">
-        <v>7210</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46223.83333333334</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="B82">
-        <v>7240</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46223.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
-        <v>7230</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46223.85416666666</v>
+        <v>46226.85416666666</v>
       </c>
       <c r="B84">
-        <v>7200</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46223.86458333334</v>
+        <v>46226.86458333334</v>
       </c>
       <c r="B85">
-        <v>7120</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46223.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>7000</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46223.88541666666</v>
+        <v>46226.88541666666</v>
       </c>
       <c r="B87">
-        <v>6880</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46223.89583333334</v>
+        <v>46226.89583333334</v>
       </c>
       <c r="B88">
-        <v>6750</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46223.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
-        <v>6590</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46223.91666666666</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="B90">
-        <v>6420</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46223.92708333334</v>
+        <v>46226.92708333334</v>
       </c>
       <c r="B91">
-        <v>6290</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46223.9375</v>
+        <v>46226.9375</v>
       </c>
       <c r="B92">
-        <v>6180</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46223.94791666666</v>
+        <v>46226.94791666666</v>
       </c>
       <c r="B93">
-        <v>6070</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46223.95833333334</v>
+        <v>46226.95833333334</v>
       </c>
       <c r="B94">
-        <v>5970</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46223.96875</v>
+        <v>46226.96875</v>
       </c>
       <c r="B95">
-        <v>5870</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46223.97916666666</v>
+        <v>46226.97916666666</v>
       </c>
       <c r="B96">
-        <v>5780</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46223.98958333334</v>
+        <v>46226.98958333334</v>
       </c>
       <c r="B97">
-        <v>5700</v>
+        <v>5440</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6FE2833C32D8D02BCEFF31D2F8375B064499DBA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3904562C-6F67-4CF3-A673-72101EA01D15}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2EF4833CE8585327A4FE31D2F8375B06F492B039" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D679A8-C84B-498F-939E-4E86617BE658}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,770 +427,770 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
-        <v>5220</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46227.010416666657</v>
+        <v>46229.010416666657</v>
       </c>
       <c r="B3">
-        <v>5170</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46227.020833333343</v>
+        <v>46229.020833333343</v>
       </c>
       <c r="B4">
-        <v>5140</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
-        <v>5100</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46227.041666666657</v>
+        <v>46229.041666666657</v>
       </c>
       <c r="B6">
-        <v>5070</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46227.052083333343</v>
+        <v>46229.052083333343</v>
       </c>
       <c r="B7">
-        <v>5030</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
-        <v>5000</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46227.072916666657</v>
+        <v>46229.072916666657</v>
       </c>
       <c r="B9">
-        <v>4990</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46227.083333333343</v>
+        <v>46229.083333333343</v>
       </c>
       <c r="B10">
-        <v>4970</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
-        <v>4960</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46227.104166666657</v>
+        <v>46229.104166666657</v>
       </c>
       <c r="B12">
-        <v>4960</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46227.114583333343</v>
+        <v>46229.114583333343</v>
       </c>
       <c r="B13">
-        <v>4970</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
-        <v>4980</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46227.135416666657</v>
+        <v>46229.135416666657</v>
       </c>
       <c r="B15">
-        <v>5010</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46227.145833333343</v>
+        <v>46229.145833333343</v>
       </c>
       <c r="B16">
-        <v>5020</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
-        <v>5030</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46227.166666666657</v>
+        <v>46229.166666666657</v>
       </c>
       <c r="B18">
-        <v>5040</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46227.177083333343</v>
+        <v>46229.177083333343</v>
       </c>
       <c r="B19">
-        <v>5060</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
-        <v>5100</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46227.197916666657</v>
+        <v>46229.197916666657</v>
       </c>
       <c r="B21">
-        <v>5150</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46227.208333333343</v>
+        <v>46229.208333333343</v>
       </c>
       <c r="B22">
-        <v>5230</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>5300</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46227.229166666657</v>
+        <v>46229.229166666657</v>
       </c>
       <c r="B24">
-        <v>5390</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46227.239583333343</v>
+        <v>46229.239583333343</v>
       </c>
       <c r="B25">
-        <v>5480</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>5560</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46227.260416666657</v>
+        <v>46229.260416666657</v>
       </c>
       <c r="B27">
-        <v>5650</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46227.270833333343</v>
+        <v>46229.270833333343</v>
       </c>
       <c r="B28">
-        <v>5720</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>5770</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46227.291666666657</v>
+        <v>46229.291666666657</v>
       </c>
       <c r="B30">
-        <v>5800</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46227.302083333343</v>
+        <v>46229.302083333343</v>
       </c>
       <c r="B31">
-        <v>5800</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>5780</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46227.322916666657</v>
+        <v>46229.322916666657</v>
       </c>
       <c r="B33">
-        <v>5730</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46227.333333333343</v>
+        <v>46229.333333333343</v>
       </c>
       <c r="B34">
-        <v>5650</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46227.34375</v>
+        <v>46229.34375</v>
       </c>
       <c r="B35">
-        <v>5560</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46227.354166666657</v>
+        <v>46229.354166666657</v>
       </c>
       <c r="B36">
-        <v>5450</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46227.364583333343</v>
+        <v>46229.364583333343</v>
       </c>
       <c r="B37">
-        <v>5330</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46227.375</v>
+        <v>46229.375</v>
       </c>
       <c r="B38">
-        <v>5210</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46227.385416666657</v>
+        <v>46229.385416666657</v>
       </c>
       <c r="B39">
-        <v>5100</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46227.395833333343</v>
+        <v>46229.395833333343</v>
       </c>
       <c r="B40">
-        <v>4990</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46227.40625</v>
+        <v>46229.40625</v>
       </c>
       <c r="B41">
-        <v>4910</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46227.416666666657</v>
+        <v>46229.416666666657</v>
       </c>
       <c r="B42">
-        <v>4830</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46227.427083333343</v>
+        <v>46229.427083333343</v>
       </c>
       <c r="B43">
-        <v>4780</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46227.4375</v>
+        <v>46229.4375</v>
       </c>
       <c r="B44">
-        <v>4740</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46227.447916666657</v>
+        <v>46229.447916666657</v>
       </c>
       <c r="B45">
-        <v>4720</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46227.458333333343</v>
+        <v>46229.458333333343</v>
       </c>
       <c r="B46">
-        <v>4720</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46227.46875</v>
+        <v>46229.46875</v>
       </c>
       <c r="B47">
-        <v>4720</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46227.479166666657</v>
+        <v>46229.479166666657</v>
       </c>
       <c r="B48">
-        <v>4730</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46227.489583333343</v>
+        <v>46229.489583333343</v>
       </c>
       <c r="B49">
-        <v>4750</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46227.5</v>
+        <v>46229.5</v>
       </c>
       <c r="B50">
-        <v>4780</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46227.510416666657</v>
+        <v>46229.510416666657</v>
       </c>
       <c r="B51">
-        <v>4810</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46227.520833333343</v>
+        <v>46229.520833333343</v>
       </c>
       <c r="B52">
-        <v>4840</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46227.53125</v>
+        <v>46229.53125</v>
       </c>
       <c r="B53">
-        <v>4870</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46227.541666666657</v>
+        <v>46229.541666666657</v>
       </c>
       <c r="B54">
-        <v>4900</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46227.552083333343</v>
+        <v>46229.552083333343</v>
       </c>
       <c r="B55">
-        <v>4940</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46227.5625</v>
+        <v>46229.5625</v>
       </c>
       <c r="B56">
-        <v>4970</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46227.572916666657</v>
+        <v>46229.572916666657</v>
       </c>
       <c r="B57">
-        <v>5010</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46227.583333333343</v>
+        <v>46229.583333333343</v>
       </c>
       <c r="B58">
-        <v>5040</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46227.59375</v>
+        <v>46229.59375</v>
       </c>
       <c r="B59">
-        <v>5080</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46227.604166666657</v>
+        <v>46229.604166666657</v>
       </c>
       <c r="B60">
-        <v>5120</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46227.614583333343</v>
+        <v>46229.614583333343</v>
       </c>
       <c r="B61">
-        <v>5170</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46227.625</v>
+        <v>46229.625</v>
       </c>
       <c r="B62">
-        <v>5230</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46227.635416666657</v>
+        <v>46229.635416666657</v>
       </c>
       <c r="B63">
-        <v>5290</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46227.645833333343</v>
+        <v>46229.645833333343</v>
       </c>
       <c r="B64">
-        <v>5370</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46227.65625</v>
+        <v>46229.65625</v>
       </c>
       <c r="B65">
-        <v>5440</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46227.666666666657</v>
+        <v>46229.666666666657</v>
       </c>
       <c r="B66">
-        <v>5510</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46227.677083333343</v>
+        <v>46229.677083333343</v>
       </c>
       <c r="B67">
-        <v>5600</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46227.6875</v>
+        <v>46229.6875</v>
       </c>
       <c r="B68">
-        <v>5670</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46227.697916666657</v>
+        <v>46229.697916666657</v>
       </c>
       <c r="B69">
-        <v>5750</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46227.708333333343</v>
+        <v>46229.708333333343</v>
       </c>
       <c r="B70">
-        <v>5830</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46227.71875</v>
+        <v>46229.71875</v>
       </c>
       <c r="B71">
-        <v>5900</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46227.729166666657</v>
+        <v>46229.729166666657</v>
       </c>
       <c r="B72">
-        <v>5980</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46227.739583333343</v>
+        <v>46229.739583333343</v>
       </c>
       <c r="B73">
-        <v>6070</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46227.75</v>
+        <v>46229.75</v>
       </c>
       <c r="B74">
-        <v>6170</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46227.760416666657</v>
+        <v>46229.760416666657</v>
       </c>
       <c r="B75">
-        <v>6260</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46227.770833333343</v>
+        <v>46229.770833333343</v>
       </c>
       <c r="B76">
-        <v>6350</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46227.78125</v>
+        <v>46229.78125</v>
       </c>
       <c r="B77">
-        <v>6430</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46227.791666666657</v>
+        <v>46229.791666666657</v>
       </c>
       <c r="B78">
-        <v>6500</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46227.802083333343</v>
+        <v>46229.802083333343</v>
       </c>
       <c r="B79">
-        <v>6550</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46227.8125</v>
+        <v>46229.8125</v>
       </c>
       <c r="B80">
-        <v>6620</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46227.822916666657</v>
+        <v>46229.822916666657</v>
       </c>
       <c r="B81">
-        <v>6670</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46227.833333333343</v>
+        <v>46229.833333333343</v>
       </c>
       <c r="B82">
-        <v>6680</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46227.84375</v>
+        <v>46229.84375</v>
       </c>
       <c r="B83">
-        <v>6660</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46227.854166666657</v>
+        <v>46229.854166666657</v>
       </c>
       <c r="B84">
-        <v>6630</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46227.864583333343</v>
+        <v>46229.864583333343</v>
       </c>
       <c r="B85">
-        <v>6580</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46227.875</v>
+        <v>46229.875</v>
       </c>
       <c r="B86">
-        <v>6480</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46227.885416666657</v>
+        <v>46229.885416666657</v>
       </c>
       <c r="B87">
-        <v>6380</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46227.895833333343</v>
+        <v>46229.895833333343</v>
       </c>
       <c r="B88">
-        <v>6250</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46227.90625</v>
+        <v>46229.90625</v>
       </c>
       <c r="B89">
-        <v>6100</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46227.916666666657</v>
+        <v>46229.916666666657</v>
       </c>
       <c r="B90">
-        <v>5960</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46227.927083333343</v>
+        <v>46229.927083333343</v>
       </c>
       <c r="B91">
-        <v>5840</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46227.9375</v>
+        <v>46229.9375</v>
       </c>
       <c r="B92">
-        <v>5710</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46227.947916666657</v>
+        <v>46229.947916666657</v>
       </c>
       <c r="B93">
-        <v>5600</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>46227.958333333343</v>
+        <v>46229.958333333343</v>
       </c>
       <c r="B94">
-        <v>5400</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>46227.96875</v>
+        <v>46229.96875</v>
       </c>
       <c r="B95">
-        <v>5310</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>46227.979166666657</v>
+        <v>46229.979166666657</v>
       </c>
       <c r="B96">
-        <v>5230</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>46227.989583333343</v>
+        <v>46229.989583333343</v>
       </c>
       <c r="B97">
-        <v>5200</v>
+        <v>4720</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2EF4833CE8585327A4FE31D2F8375B06F492B039" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D679A8-C84B-498F-939E-4E86617BE658}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,772 +392,772 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
-        <v>4830</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46229.010416666657</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
-        <v>4780</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46229.020833333343</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
-        <v>4730</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
-        <v>4680</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46229.041666666657</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
-        <v>4650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46229.052083333343</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
-        <v>4610</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
-        <v>4580</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46229.072916666657</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
-        <v>4560</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46229.083333333343</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
-        <v>4550</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
-        <v>4540</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46229.104166666657</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
-        <v>4540</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46229.114583333343</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
-        <v>4530</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
-        <v>4520</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46229.135416666657</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46229.145833333343</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
-        <v>4480</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
-        <v>4470</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46229.166666666657</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
-        <v>4460</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46229.177083333343</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
-        <v>4440</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
-        <v>4430</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46229.197916666657</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
-        <v>4410</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46229.208333333343</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>4350</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46229.229166666657</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>4320</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46229.239583333343</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>4280</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>4230</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46229.260416666657</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>4170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46229.270833333343</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>4030</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46229.291666666657</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>3960</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46229.302083333343</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>3880</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>3790</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5830</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46229.322916666657</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
-        <v>3710</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5770</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46229.333333333343</v>
+        <v>46246.33333333334</v>
       </c>
       <c r="B34">
-        <v>3620</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5710</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46229.34375</v>
+        <v>46246.34375</v>
       </c>
       <c r="B35">
-        <v>3540</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46229.354166666657</v>
+        <v>46246.35416666666</v>
       </c>
       <c r="B36">
-        <v>3460</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5520</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46229.364583333343</v>
+        <v>46246.36458333334</v>
       </c>
       <c r="B37">
-        <v>3390</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46229.375</v>
+        <v>46246.375</v>
       </c>
       <c r="B38">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46229.385416666657</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="B39">
-        <v>3280</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46229.395833333343</v>
+        <v>46246.39583333334</v>
       </c>
       <c r="B40">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46229.40625</v>
+        <v>46246.40625</v>
       </c>
       <c r="B41">
-        <v>3210</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46229.416666666657</v>
+        <v>46246.41666666666</v>
       </c>
       <c r="B42">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46229.427083333343</v>
+        <v>46246.42708333334</v>
       </c>
       <c r="B43">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46229.4375</v>
+        <v>46246.4375</v>
       </c>
       <c r="B44">
-        <v>3210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46229.447916666657</v>
+        <v>46246.44791666666</v>
       </c>
       <c r="B45">
-        <v>3220</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46229.458333333343</v>
+        <v>46246.45833333334</v>
       </c>
       <c r="B46">
-        <v>3230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46229.46875</v>
+        <v>46246.46875</v>
       </c>
       <c r="B47">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46229.479166666657</v>
+        <v>46246.47916666666</v>
       </c>
       <c r="B48">
-        <v>3270</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46229.489583333343</v>
+        <v>46246.48958333334</v>
       </c>
       <c r="B49">
-        <v>3280</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4870</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46229.5</v>
+        <v>46246.5</v>
       </c>
       <c r="B50">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4920</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46229.510416666657</v>
+        <v>46246.51041666666</v>
       </c>
       <c r="B51">
-        <v>3310</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46229.520833333343</v>
+        <v>46246.52083333334</v>
       </c>
       <c r="B52">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46229.53125</v>
+        <v>46246.53125</v>
       </c>
       <c r="B53">
-        <v>3350</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46229.541666666657</v>
+        <v>46246.54166666666</v>
       </c>
       <c r="B54">
-        <v>3370</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46229.552083333343</v>
+        <v>46246.55208333334</v>
       </c>
       <c r="B55">
-        <v>3390</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46229.5625</v>
+        <v>46246.5625</v>
       </c>
       <c r="B56">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46229.572916666657</v>
+        <v>46246.57291666666</v>
       </c>
       <c r="B57">
-        <v>3460</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46229.583333333343</v>
+        <v>46246.58333333334</v>
       </c>
       <c r="B58">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46229.59375</v>
+        <v>46246.59375</v>
       </c>
       <c r="B59">
-        <v>3540</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46229.604166666657</v>
+        <v>46246.60416666666</v>
       </c>
       <c r="B60">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5270</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46229.614583333343</v>
+        <v>46246.61458333334</v>
       </c>
       <c r="B61">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46229.625</v>
+        <v>46246.625</v>
       </c>
       <c r="B62">
-        <v>3730</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46229.635416666657</v>
+        <v>46246.63541666666</v>
       </c>
       <c r="B63">
-        <v>3810</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5520</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46229.645833333343</v>
+        <v>46246.64583333334</v>
       </c>
       <c r="B64">
-        <v>3910</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5630</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46229.65625</v>
+        <v>46246.65625</v>
       </c>
       <c r="B65">
-        <v>4020</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46229.666666666657</v>
+        <v>46246.66666666666</v>
       </c>
       <c r="B66">
-        <v>4140</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46229.677083333343</v>
+        <v>46246.67708333334</v>
       </c>
       <c r="B67">
-        <v>4260</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46229.6875</v>
+        <v>46246.6875</v>
       </c>
       <c r="B68">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46229.697916666657</v>
+        <v>46246.69791666666</v>
       </c>
       <c r="B69">
-        <v>4480</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46229.708333333343</v>
+        <v>46246.70833333334</v>
       </c>
       <c r="B70">
-        <v>4610</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6370</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46229.71875</v>
+        <v>46246.71875</v>
       </c>
       <c r="B71">
-        <v>4730</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6490</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46229.729166666657</v>
+        <v>46246.72916666666</v>
       </c>
       <c r="B72">
-        <v>4840</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6610</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46229.739583333343</v>
+        <v>46246.73958333334</v>
       </c>
       <c r="B73">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46229.75</v>
+        <v>46246.75</v>
       </c>
       <c r="B74">
-        <v>5050</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6870</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46229.760416666657</v>
+        <v>46246.76041666666</v>
       </c>
       <c r="B75">
-        <v>5170</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6980</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46229.770833333343</v>
+        <v>46246.77083333334</v>
       </c>
       <c r="B76">
-        <v>5270</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46229.78125</v>
+        <v>46246.78125</v>
       </c>
       <c r="B77">
-        <v>5360</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7090</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46229.791666666657</v>
+        <v>46246.79166666666</v>
       </c>
       <c r="B78">
-        <v>5450</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46229.802083333343</v>
+        <v>46246.80208333334</v>
       </c>
       <c r="B79">
-        <v>5530</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46229.8125</v>
+        <v>46246.8125</v>
       </c>
       <c r="B80">
+        <v>7140</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46246.82291666666</v>
+      </c>
+      <c r="B81">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
+        <v>46246.83333333334</v>
+      </c>
+      <c r="B82">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
+        <v>46246.84375</v>
+      </c>
+      <c r="B83">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>46246.85416666666</v>
+      </c>
+      <c r="B84">
+        <v>7130</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
+        <v>46246.86458333334</v>
+      </c>
+      <c r="B85">
+        <v>7020</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2">
+        <v>46246.875</v>
+      </c>
+      <c r="B86">
+        <v>6840</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2">
+        <v>46246.88541666666</v>
+      </c>
+      <c r="B87">
+        <v>6670</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2">
+        <v>46246.89583333334</v>
+      </c>
+      <c r="B88">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
+        <v>46246.90625</v>
+      </c>
+      <c r="B89">
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
+        <v>46246.91666666666</v>
+      </c>
+      <c r="B90">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
+        <v>46246.92708333334</v>
+      </c>
+      <c r="B91">
+        <v>6070</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46246.9375</v>
+      </c>
+      <c r="B92">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46246.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46246.95833333334</v>
+      </c>
+      <c r="B94">
         <v>5610</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
-        <v>46229.822916666657</v>
-      </c>
-      <c r="B81">
-        <v>5670</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>46229.833333333343</v>
-      </c>
-      <c r="B82">
-        <v>5710</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>46229.84375</v>
-      </c>
-      <c r="B83">
-        <v>5750</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>46229.854166666657</v>
-      </c>
-      <c r="B84">
-        <v>5760</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>46229.864583333343</v>
-      </c>
-      <c r="B85">
-        <v>5750</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>46229.875</v>
-      </c>
-      <c r="B86">
-        <v>5710</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>46229.885416666657</v>
-      </c>
-      <c r="B87">
-        <v>5660</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>46229.895833333343</v>
-      </c>
-      <c r="B88">
-        <v>5560</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>46229.90625</v>
-      </c>
-      <c r="B89">
-        <v>5450</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>46229.916666666657</v>
-      </c>
-      <c r="B90">
-        <v>5350</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>46229.927083333343</v>
-      </c>
-      <c r="B91">
-        <v>5240</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>46229.9375</v>
-      </c>
-      <c r="B92">
-        <v>5120</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>46229.947916666657</v>
-      </c>
-      <c r="B93">
-        <v>5020</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>46229.958333333343</v>
-      </c>
-      <c r="B94">
-        <v>4900</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46229.96875</v>
+        <v>46246.96875</v>
       </c>
       <c r="B95">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46229.979166666657</v>
+        <v>46246.97916666666</v>
       </c>
       <c r="B96">
-        <v>4780</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46229.989583333343</v>
+        <v>46246.98958333334</v>
       </c>
       <c r="B97">
-        <v>4720</v>
+        <v>5440</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B2">
-        <v>5520</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46251.01041666666</v>
       </c>
       <c r="B3">
-        <v>5460</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46251.02083333334</v>
       </c>
       <c r="B4">
-        <v>5400</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46251.03125</v>
       </c>
       <c r="B5">
-        <v>5340</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46251.04166666666</v>
       </c>
       <c r="B6">
-        <v>5290</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46251.05208333334</v>
       </c>
       <c r="B7">
-        <v>5250</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46251.0625</v>
       </c>
       <c r="B8">
-        <v>5220</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46251.07291666666</v>
       </c>
       <c r="B9">
-        <v>5200</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46251.08333333334</v>
       </c>
       <c r="B10">
-        <v>5180</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46251.09375</v>
       </c>
       <c r="B11">
-        <v>5180</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46251.10416666666</v>
       </c>
       <c r="B12">
-        <v>5180</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46251.11458333334</v>
       </c>
       <c r="B13">
-        <v>5190</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46251.125</v>
       </c>
       <c r="B14">
-        <v>5250</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46251.13541666666</v>
       </c>
       <c r="B15">
-        <v>5250</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46251.14583333334</v>
       </c>
       <c r="B16">
-        <v>5250</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46251.15625</v>
       </c>
       <c r="B17">
-        <v>5250</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46251.16666666666</v>
       </c>
       <c r="B18">
-        <v>5250</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46251.17708333334</v>
       </c>
       <c r="B19">
-        <v>5250</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46251.1875</v>
       </c>
       <c r="B20">
-        <v>5250</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46251.19791666666</v>
       </c>
       <c r="B21">
-        <v>5260</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46251.20833333334</v>
       </c>
       <c r="B22">
-        <v>5320</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46251.21875</v>
       </c>
       <c r="B23">
-        <v>5390</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46251.22916666666</v>
       </c>
       <c r="B24">
-        <v>5460</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="B25">
-        <v>5550</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46251.25</v>
       </c>
       <c r="B26">
-        <v>5690</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46251.26041666666</v>
       </c>
       <c r="B27">
-        <v>5800</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46251.27083333334</v>
       </c>
       <c r="B28">
-        <v>5870</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46251.28125</v>
       </c>
       <c r="B29">
-        <v>5900</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46251.29166666666</v>
       </c>
       <c r="B30">
-        <v>5900</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46251.30208333334</v>
       </c>
       <c r="B31">
-        <v>5870</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46251.3125</v>
       </c>
       <c r="B32">
-        <v>5830</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46251.32291666666</v>
       </c>
       <c r="B33">
-        <v>5770</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="B34">
-        <v>5710</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46251.34375</v>
       </c>
       <c r="B35">
-        <v>5620</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46246.35416666666</v>
+        <v>46251.35416666666</v>
       </c>
       <c r="B36">
-        <v>5520</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46246.36458333334</v>
+        <v>46251.36458333334</v>
       </c>
       <c r="B37">
-        <v>5420</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46246.375</v>
+        <v>46251.375</v>
       </c>
       <c r="B38">
-        <v>5300</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46246.38541666666</v>
+        <v>46251.38541666666</v>
       </c>
       <c r="B39">
-        <v>5210</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46246.39583333334</v>
+        <v>46251.39583333334</v>
       </c>
       <c r="B40">
-        <v>5120</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46246.40625</v>
+        <v>46251.40625</v>
       </c>
       <c r="B41">
-        <v>5050</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46246.41666666666</v>
+        <v>46251.41666666666</v>
       </c>
       <c r="B42">
-        <v>4980</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46246.42708333334</v>
+        <v>46251.42708333334</v>
       </c>
       <c r="B43">
-        <v>4940</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46246.4375</v>
+        <v>46251.4375</v>
       </c>
       <c r="B44">
-        <v>4910</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46246.44791666666</v>
+        <v>46251.44791666666</v>
       </c>
       <c r="B45">
-        <v>4890</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46246.45833333334</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="B46">
-        <v>4860</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46246.46875</v>
+        <v>46251.46875</v>
       </c>
       <c r="B47">
-        <v>4860</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46246.47916666666</v>
+        <v>46251.47916666666</v>
       </c>
       <c r="B48">
-        <v>4860</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46246.48958333334</v>
+        <v>46251.48958333334</v>
       </c>
       <c r="B49">
-        <v>4870</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46246.5</v>
+        <v>46251.5</v>
       </c>
       <c r="B50">
-        <v>4920</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46246.51041666666</v>
+        <v>46251.51041666666</v>
       </c>
       <c r="B51">
-        <v>4960</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46246.52083333334</v>
+        <v>46251.52083333334</v>
       </c>
       <c r="B52">
-        <v>4990</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46246.53125</v>
+        <v>46251.53125</v>
       </c>
       <c r="B53">
-        <v>5000</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46246.54166666666</v>
+        <v>46251.54166666666</v>
       </c>
       <c r="B54">
-        <v>5030</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46246.55208333334</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="B55">
-        <v>5060</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46246.5625</v>
+        <v>46251.5625</v>
       </c>
       <c r="B56">
-        <v>5090</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46246.57291666666</v>
+        <v>46251.57291666666</v>
       </c>
       <c r="B57">
-        <v>5120</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46246.58333333334</v>
+        <v>46251.58333333334</v>
       </c>
       <c r="B58">
-        <v>5170</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46246.59375</v>
+        <v>46251.59375</v>
       </c>
       <c r="B59">
-        <v>5220</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46246.60416666666</v>
+        <v>46251.60416666666</v>
       </c>
       <c r="B60">
-        <v>5270</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46246.61458333334</v>
+        <v>46251.61458333334</v>
       </c>
       <c r="B61">
-        <v>5340</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46246.625</v>
+        <v>46251.625</v>
       </c>
       <c r="B62">
-        <v>5420</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46246.63541666666</v>
+        <v>46251.63541666666</v>
       </c>
       <c r="B63">
-        <v>5520</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46246.64583333334</v>
+        <v>46251.64583333334</v>
       </c>
       <c r="B64">
-        <v>5630</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46246.65625</v>
+        <v>46251.65625</v>
       </c>
       <c r="B65">
-        <v>5750</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46246.66666666666</v>
+        <v>46251.66666666666</v>
       </c>
       <c r="B66">
-        <v>5870</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46246.67708333334</v>
+        <v>46251.67708333334</v>
       </c>
       <c r="B67">
-        <v>6000</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46246.6875</v>
+        <v>46251.6875</v>
       </c>
       <c r="B68">
-        <v>6110</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46246.69791666666</v>
+        <v>46251.69791666666</v>
       </c>
       <c r="B69">
-        <v>6230</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46246.70833333334</v>
+        <v>46251.70833333334</v>
       </c>
       <c r="B70">
-        <v>6370</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46246.71875</v>
+        <v>46251.71875</v>
       </c>
       <c r="B71">
-        <v>6490</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46246.72916666666</v>
+        <v>46251.72916666666</v>
       </c>
       <c r="B72">
-        <v>6610</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46246.73958333334</v>
+        <v>46251.73958333334</v>
       </c>
       <c r="B73">
-        <v>6750</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46246.75</v>
+        <v>46251.75</v>
       </c>
       <c r="B74">
-        <v>6870</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46246.76041666666</v>
+        <v>46251.76041666666</v>
       </c>
       <c r="B75">
-        <v>6980</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46246.77083333334</v>
+        <v>46251.77083333334</v>
       </c>
       <c r="B76">
-        <v>7060</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46246.78125</v>
+        <v>46251.78125</v>
       </c>
       <c r="B77">
-        <v>7090</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46246.79166666666</v>
+        <v>46251.79166666666</v>
       </c>
       <c r="B78">
-        <v>7100</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46246.80208333334</v>
+        <v>46251.80208333334</v>
       </c>
       <c r="B79">
-        <v>7120</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46246.8125</v>
+        <v>46251.8125</v>
       </c>
       <c r="B80">
-        <v>7140</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46246.82291666666</v>
+        <v>46251.82291666666</v>
       </c>
       <c r="B81">
-        <v>7180</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46246.83333333334</v>
+        <v>46251.83333333334</v>
       </c>
       <c r="B82">
-        <v>7190</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46246.84375</v>
+        <v>46251.84375</v>
       </c>
       <c r="B83">
-        <v>7180</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46246.85416666666</v>
+        <v>46251.85416666666</v>
       </c>
       <c r="B84">
-        <v>7130</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46246.86458333334</v>
+        <v>46251.86458333334</v>
       </c>
       <c r="B85">
-        <v>7020</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46246.875</v>
+        <v>46251.875</v>
       </c>
       <c r="B86">
-        <v>6840</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46246.88541666666</v>
+        <v>46251.88541666666</v>
       </c>
       <c r="B87">
-        <v>6670</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46246.89583333334</v>
+        <v>46251.89583333334</v>
       </c>
       <c r="B88">
-        <v>6530</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46246.90625</v>
+        <v>46251.90625</v>
       </c>
       <c r="B89">
-        <v>6380</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46246.91666666666</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="B90">
-        <v>6210</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46246.92708333334</v>
+        <v>46251.92708333334</v>
       </c>
       <c r="B91">
-        <v>6070</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46246.9375</v>
+        <v>46251.9375</v>
       </c>
       <c r="B92">
-        <v>5960</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46246.94791666666</v>
+        <v>46251.94791666666</v>
       </c>
       <c r="B93">
-        <v>5850</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46246.95833333334</v>
+        <v>46251.95833333334</v>
       </c>
       <c r="B94">
-        <v>5610</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46246.96875</v>
+        <v>46251.96875</v>
       </c>
       <c r="B95">
-        <v>5570</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46246.97916666666</v>
+        <v>46251.97916666666</v>
       </c>
       <c r="B96">
-        <v>5510</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46246.98958333334</v>
+        <v>46251.98958333334</v>
       </c>
       <c r="B97">
-        <v>5440</v>
+        <v>5270</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,631 +394,631 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2">
-        <v>4620</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46251.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
-        <v>4560</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46251.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
-        <v>4530</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46251.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
-        <v>4500</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46251.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
-        <v>4460</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46251.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
-        <v>4430</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46251.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
-        <v>4420</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46251.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
-        <v>4410</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46251.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
-        <v>4400</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46251.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
-        <v>4400</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46251.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
-        <v>4400</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46251.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
-        <v>4410</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46251.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
-        <v>4440</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46251.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
-        <v>4450</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46251.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
-        <v>4450</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46251.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
-        <v>4460</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46251.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
-        <v>4490</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46251.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
-        <v>4530</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46251.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
-        <v>4590</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46251.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
-        <v>4680</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46251.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
-        <v>4760</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46251.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
-        <v>4870</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46251.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>4990</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>5120</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46251.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>5310</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46251.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>5440</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46251.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>5510</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46251.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>5550</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46251.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>5570</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46251.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>5560</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46251.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>5550</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46251.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
       <c r="B33">
-        <v>5510</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46251.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B34">
-        <v>5350</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46251.34375</v>
+        <v>46252.34375</v>
       </c>
       <c r="B35">
-        <v>5170</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46251.35416666666</v>
+        <v>46252.35416666666</v>
       </c>
       <c r="B36">
-        <v>5020</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46251.36458333334</v>
+        <v>46252.36458333334</v>
       </c>
       <c r="B37">
-        <v>4890</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46251.375</v>
+        <v>46252.375</v>
       </c>
       <c r="B38">
-        <v>4780</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46251.38541666666</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="B39">
-        <v>4680</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46251.39583333334</v>
+        <v>46252.39583333334</v>
       </c>
       <c r="B40">
-        <v>4590</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46251.40625</v>
+        <v>46252.40625</v>
       </c>
       <c r="B41">
-        <v>4510</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46251.41666666666</v>
+        <v>46252.41666666666</v>
       </c>
       <c r="B42">
-        <v>4420</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46251.42708333334</v>
+        <v>46252.42708333334</v>
       </c>
       <c r="B43">
-        <v>4400</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46251.4375</v>
+        <v>46252.4375</v>
       </c>
       <c r="B44">
-        <v>4400</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46251.44791666666</v>
+        <v>46252.44791666666</v>
       </c>
       <c r="B45">
-        <v>4400</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46251.45833333334</v>
+        <v>46252.45833333334</v>
       </c>
       <c r="B46">
-        <v>4420</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46251.46875</v>
+        <v>46252.46875</v>
       </c>
       <c r="B47">
-        <v>4430</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46251.47916666666</v>
+        <v>46252.47916666666</v>
       </c>
       <c r="B48">
-        <v>4440</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46251.48958333334</v>
+        <v>46252.48958333334</v>
       </c>
       <c r="B49">
-        <v>4450</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46251.5</v>
+        <v>46252.5</v>
       </c>
       <c r="B50">
-        <v>4490</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46251.51041666666</v>
+        <v>46252.51041666666</v>
       </c>
       <c r="B51">
-        <v>4510</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46251.52083333334</v>
+        <v>46252.52083333334</v>
       </c>
       <c r="B52">
-        <v>4540</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46251.53125</v>
+        <v>46252.53125</v>
       </c>
       <c r="B53">
-        <v>4570</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46251.54166666666</v>
+        <v>46252.54166666666</v>
       </c>
       <c r="B54">
-        <v>4600</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46251.55208333334</v>
+        <v>46252.55208333334</v>
       </c>
       <c r="B55">
-        <v>4650</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46251.5625</v>
+        <v>46252.5625</v>
       </c>
       <c r="B56">
-        <v>4700</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46251.57291666666</v>
+        <v>46252.57291666666</v>
       </c>
       <c r="B57">
-        <v>4760</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46251.58333333334</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="B58">
-        <v>4820</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46251.59375</v>
+        <v>46252.59375</v>
       </c>
       <c r="B59">
-        <v>4870</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46251.60416666666</v>
+        <v>46252.60416666666</v>
       </c>
       <c r="B60">
-        <v>4920</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46251.61458333334</v>
+        <v>46252.61458333334</v>
       </c>
       <c r="B61">
-        <v>4990</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46251.625</v>
+        <v>46252.625</v>
       </c>
       <c r="B62">
-        <v>5070</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46251.63541666666</v>
+        <v>46252.63541666666</v>
       </c>
       <c r="B63">
-        <v>5160</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46251.64583333334</v>
+        <v>46252.64583333334</v>
       </c>
       <c r="B64">
-        <v>5280</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46251.65625</v>
+        <v>46252.65625</v>
       </c>
       <c r="B65">
-        <v>5410</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46251.66666666666</v>
+        <v>46252.66666666666</v>
       </c>
       <c r="B66">
-        <v>5540</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46251.67708333334</v>
+        <v>46252.67708333334</v>
       </c>
       <c r="B67">
-        <v>5690</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46251.6875</v>
+        <v>46252.6875</v>
       </c>
       <c r="B68">
-        <v>5830</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46251.69791666666</v>
+        <v>46252.69791666666</v>
       </c>
       <c r="B69">
-        <v>5970</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46251.70833333334</v>
+        <v>46252.70833333334</v>
       </c>
       <c r="B70">
-        <v>6150</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46251.71875</v>
+        <v>46252.71875</v>
       </c>
       <c r="B71">
-        <v>6270</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46251.72916666666</v>
+        <v>46252.72916666666</v>
       </c>
       <c r="B72">
-        <v>6380</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46251.73958333334</v>
+        <v>46252.73958333334</v>
       </c>
       <c r="B73">
-        <v>6500</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46251.75</v>
+        <v>46252.75</v>
       </c>
       <c r="B74">
-        <v>6580</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46251.76041666666</v>
+        <v>46252.76041666666</v>
       </c>
       <c r="B75">
-        <v>6650</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46251.77083333334</v>
+        <v>46252.77083333334</v>
       </c>
       <c r="B76">
-        <v>6720</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46251.78125</v>
+        <v>46252.78125</v>
       </c>
       <c r="B77">
-        <v>6770</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46251.79166666666</v>
+        <v>46252.79166666666</v>
       </c>
       <c r="B78">
-        <v>6820</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46251.80208333334</v>
+        <v>46252.80208333334</v>
       </c>
       <c r="B79">
-        <v>6870</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46251.8125</v>
+        <v>46252.8125</v>
       </c>
       <c r="B80">
         <v>6900</v>
@@ -1026,138 +1026,138 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46251.82291666666</v>
+        <v>46252.82291666666</v>
       </c>
       <c r="B81">
-        <v>6950</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46251.83333333334</v>
+        <v>46252.83333333334</v>
       </c>
       <c r="B82">
-        <v>6970</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46251.84375</v>
+        <v>46252.84375</v>
       </c>
       <c r="B83">
-        <v>6960</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46251.85416666666</v>
+        <v>46252.85416666666</v>
       </c>
       <c r="B84">
-        <v>6910</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46251.86458333334</v>
+        <v>46252.86458333334</v>
       </c>
       <c r="B85">
-        <v>6760</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46251.875</v>
+        <v>46252.875</v>
       </c>
       <c r="B86">
-        <v>6550</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46251.88541666666</v>
+        <v>46252.88541666666</v>
       </c>
       <c r="B87">
-        <v>6360</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46251.89583333334</v>
+        <v>46252.89583333334</v>
       </c>
       <c r="B88">
-        <v>6190</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46251.90625</v>
+        <v>46252.90625</v>
       </c>
       <c r="B89">
-        <v>6040</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46251.91666666666</v>
+        <v>46252.91666666666</v>
       </c>
       <c r="B90">
-        <v>5880</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46251.92708333334</v>
+        <v>46252.92708333334</v>
       </c>
       <c r="B91">
-        <v>5720</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46251.9375</v>
+        <v>46252.9375</v>
       </c>
       <c r="B92">
-        <v>5610</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46251.94791666666</v>
+        <v>46252.94791666666</v>
       </c>
       <c r="B93">
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46251.95833333334</v>
+        <v>46252.95833333334</v>
       </c>
       <c r="B94">
-        <v>5450</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46251.96875</v>
+        <v>46252.96875</v>
       </c>
       <c r="B95">
-        <v>5380</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46251.97916666666</v>
+        <v>46252.97916666666</v>
       </c>
       <c r="B96">
-        <v>5330</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46251.98958333334</v>
+        <v>46252.98958333334</v>
       </c>
       <c r="B97">
-        <v>5270</v>
+        <v>5310</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B2">
-        <v>5140</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46259.01041666666</v>
       </c>
       <c r="B3">
-        <v>5080</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46259.02083333334</v>
       </c>
       <c r="B4">
-        <v>5040</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46259.03125</v>
       </c>
       <c r="B5">
-        <v>5010</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="B6">
-        <v>4980</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46259.05208333334</v>
       </c>
       <c r="B7">
-        <v>4960</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46259.0625</v>
       </c>
       <c r="B8">
-        <v>4930</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46259.07291666666</v>
       </c>
       <c r="B9">
-        <v>4930</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46259.08333333334</v>
       </c>
       <c r="B10">
-        <v>4930</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46259.09375</v>
       </c>
       <c r="B11">
-        <v>4930</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46259.10416666666</v>
       </c>
       <c r="B12">
-        <v>4940</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46259.11458333334</v>
       </c>
       <c r="B13">
-        <v>4950</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46259.125</v>
       </c>
       <c r="B14">
-        <v>4980</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46259.13541666666</v>
       </c>
       <c r="B15">
-        <v>4990</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46259.14583333334</v>
       </c>
       <c r="B16">
-        <v>4990</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46259.15625</v>
       </c>
       <c r="B17">
-        <v>5000</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46259.16666666666</v>
       </c>
       <c r="B18">
-        <v>5020</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46259.17708333334</v>
       </c>
       <c r="B19">
-        <v>5040</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46259.1875</v>
       </c>
       <c r="B20">
-        <v>5080</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46259.19791666666</v>
       </c>
       <c r="B21">
-        <v>5130</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46259.20833333334</v>
       </c>
       <c r="B22">
-        <v>5200</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46259.21875</v>
       </c>
       <c r="B23">
-        <v>5270</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46259.22916666666</v>
       </c>
       <c r="B24">
-        <v>5350</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46259.23958333334</v>
       </c>
       <c r="B25">
-        <v>5440</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46259.25</v>
       </c>
       <c r="B26">
-        <v>5530</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46259.26041666666</v>
       </c>
       <c r="B27">
-        <v>5610</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46259.27083333334</v>
       </c>
       <c r="B28">
-        <v>5680</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46259.28125</v>
       </c>
       <c r="B29">
-        <v>5740</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46259.29166666666</v>
       </c>
       <c r="B30">
-        <v>5770</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46259.30208333334</v>
       </c>
       <c r="B31">
-        <v>5790</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46252.3125</v>
+        <v>46259.3125</v>
       </c>
       <c r="B32">
-        <v>5780</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46252.32291666666</v>
+        <v>46259.32291666666</v>
       </c>
       <c r="B33">
-        <v>5750</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46252.33333333334</v>
+        <v>46259.33333333334</v>
       </c>
       <c r="B34">
-        <v>5700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46252.34375</v>
+        <v>46259.34375</v>
       </c>
       <c r="B35">
-        <v>5630</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46252.35416666666</v>
+        <v>46259.35416666666</v>
       </c>
       <c r="B36">
-        <v>5550</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46252.36458333334</v>
+        <v>46259.36458333334</v>
       </c>
       <c r="B37">
-        <v>5460</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46252.375</v>
+        <v>46259.375</v>
       </c>
       <c r="B38">
-        <v>5370</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46252.38541666666</v>
+        <v>46259.38541666666</v>
       </c>
       <c r="B39">
-        <v>5280</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46252.39583333334</v>
+        <v>46259.39583333334</v>
       </c>
       <c r="B40">
-        <v>5200</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46252.40625</v>
+        <v>46259.40625</v>
       </c>
       <c r="B41">
-        <v>5130</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46252.41666666666</v>
+        <v>46259.41666666666</v>
       </c>
       <c r="B42">
-        <v>5070</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46252.42708333334</v>
+        <v>46259.42708333334</v>
       </c>
       <c r="B43">
-        <v>5020</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46252.4375</v>
+        <v>46259.4375</v>
       </c>
       <c r="B44">
-        <v>4980</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46252.44791666666</v>
+        <v>46259.44791666666</v>
       </c>
       <c r="B45">
-        <v>4950</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46252.45833333334</v>
+        <v>46259.45833333334</v>
       </c>
       <c r="B46">
-        <v>4930</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46252.46875</v>
+        <v>46259.46875</v>
       </c>
       <c r="B47">
-        <v>4920</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46252.47916666666</v>
+        <v>46259.47916666666</v>
       </c>
       <c r="B48">
-        <v>4910</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46252.48958333334</v>
+        <v>46259.48958333334</v>
       </c>
       <c r="B49">
-        <v>4920</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46252.5</v>
+        <v>46259.5</v>
       </c>
       <c r="B50">
-        <v>4940</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46252.51041666666</v>
+        <v>46259.51041666666</v>
       </c>
       <c r="B51">
-        <v>4960</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46252.52083333334</v>
+        <v>46259.52083333334</v>
       </c>
       <c r="B52">
-        <v>4990</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46252.53125</v>
+        <v>46259.53125</v>
       </c>
       <c r="B53">
-        <v>5030</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46252.54166666666</v>
+        <v>46259.54166666666</v>
       </c>
       <c r="B54">
-        <v>5070</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46252.55208333334</v>
+        <v>46259.55208333334</v>
       </c>
       <c r="B55">
-        <v>5110</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46252.5625</v>
+        <v>46259.5625</v>
       </c>
       <c r="B56">
-        <v>5150</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46252.57291666666</v>
+        <v>46259.57291666666</v>
       </c>
       <c r="B57">
-        <v>5190</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46252.58333333334</v>
+        <v>46259.58333333334</v>
       </c>
       <c r="B58">
-        <v>5220</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46252.59375</v>
+        <v>46259.59375</v>
       </c>
       <c r="B59">
-        <v>5250</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46252.60416666666</v>
+        <v>46259.60416666666</v>
       </c>
       <c r="B60">
-        <v>5280</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46252.61458333334</v>
+        <v>46259.61458333334</v>
       </c>
       <c r="B61">
-        <v>5320</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46252.625</v>
+        <v>46259.625</v>
       </c>
       <c r="B62">
-        <v>5380</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46252.63541666666</v>
+        <v>46259.63541666666</v>
       </c>
       <c r="B63">
-        <v>5450</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46252.64583333334</v>
+        <v>46259.64583333334</v>
       </c>
       <c r="B64">
-        <v>5520</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46252.65625</v>
+        <v>46259.65625</v>
       </c>
       <c r="B65">
-        <v>5600</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46252.66666666666</v>
+        <v>46259.66666666666</v>
       </c>
       <c r="B66">
-        <v>5700</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46252.67708333334</v>
+        <v>46259.67708333334</v>
       </c>
       <c r="B67">
-        <v>5800</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46252.6875</v>
+        <v>46259.6875</v>
       </c>
       <c r="B68">
-        <v>5900</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46252.69791666666</v>
+        <v>46259.69791666666</v>
       </c>
       <c r="B69">
-        <v>6000</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46252.70833333334</v>
+        <v>46259.70833333334</v>
       </c>
       <c r="B70">
-        <v>6100</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46252.71875</v>
+        <v>46259.71875</v>
       </c>
       <c r="B71">
-        <v>6200</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46252.72916666666</v>
+        <v>46259.72916666666</v>
       </c>
       <c r="B72">
-        <v>6300</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46252.73958333334</v>
+        <v>46259.73958333334</v>
       </c>
       <c r="B73">
-        <v>6410</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46252.75</v>
+        <v>46259.75</v>
       </c>
       <c r="B74">
-        <v>6480</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46252.76041666666</v>
+        <v>46259.76041666666</v>
       </c>
       <c r="B75">
-        <v>6580</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46252.77083333334</v>
+        <v>46259.77083333334</v>
       </c>
       <c r="B76">
-        <v>6660</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46252.78125</v>
+        <v>46259.78125</v>
       </c>
       <c r="B77">
-        <v>6720</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46252.79166666666</v>
+        <v>46259.79166666666</v>
       </c>
       <c r="B78">
-        <v>6790</v>
+        <v>7060</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46252.80208333334</v>
+        <v>46259.80208333334</v>
       </c>
       <c r="B79">
-        <v>6850</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46252.8125</v>
+        <v>46259.8125</v>
       </c>
       <c r="B80">
-        <v>6900</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46252.82291666666</v>
+        <v>46259.82291666666</v>
       </c>
       <c r="B81">
-        <v>6930</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46252.83333333334</v>
+        <v>46259.83333333334</v>
       </c>
       <c r="B82">
-        <v>6940</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46252.84375</v>
+        <v>46259.84375</v>
       </c>
       <c r="B83">
-        <v>6920</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46252.85416666666</v>
+        <v>46259.85416666666</v>
       </c>
       <c r="B84">
-        <v>6870</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46252.86458333334</v>
+        <v>46259.86458333334</v>
       </c>
       <c r="B85">
-        <v>6740</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46252.875</v>
+        <v>46259.875</v>
       </c>
       <c r="B86">
-        <v>6590</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46252.88541666666</v>
+        <v>46259.88541666666</v>
       </c>
       <c r="B87">
-        <v>6450</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46252.89583333334</v>
+        <v>46259.89583333334</v>
       </c>
       <c r="B88">
-        <v>6300</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46252.90625</v>
+        <v>46259.90625</v>
       </c>
       <c r="B89">
-        <v>6150</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46252.91666666666</v>
+        <v>46259.91666666666</v>
       </c>
       <c r="B90">
-        <v>6000</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46252.92708333334</v>
+        <v>46259.92708333334</v>
       </c>
       <c r="B91">
-        <v>5850</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46252.9375</v>
+        <v>46259.9375</v>
       </c>
       <c r="B92">
-        <v>5730</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46252.94791666666</v>
+        <v>46259.94791666666</v>
       </c>
       <c r="B93">
-        <v>5600</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46252.95833333334</v>
+        <v>46259.95833333334</v>
       </c>
       <c r="B94">
         <v>5500</v>
@@ -1138,15 +1138,15 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46252.96875</v>
+        <v>46259.96875</v>
       </c>
       <c r="B95">
-        <v>5450</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46252.97916666666</v>
+        <v>46259.97916666666</v>
       </c>
       <c r="B96">
         <v>5390</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46252.98958333334</v>
+        <v>46259.98958333334</v>
       </c>
       <c r="B97">
-        <v>5310</v>
+        <v>5330</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,135 +394,135 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
-        <v>5280</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
-        <v>5190</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
-        <v>5130</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
-        <v>5090</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
-        <v>5040</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
-        <v>5020</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
-        <v>5020</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
-        <v>5000</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
-        <v>5000</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
-        <v>5000</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
-        <v>5000</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
-        <v>5030</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
-        <v>5090</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
-        <v>5120</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
-        <v>5150</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
-        <v>5170</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
         <v>5220</v>
@@ -530,15 +530,15 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
-        <v>5240</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
         <v>5260</v>
@@ -546,618 +546,618 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
-        <v>5280</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
-        <v>5290</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
-        <v>5300</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
-        <v>5300</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
-        <v>5350</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
-        <v>5550</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>5680</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>5750</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>5820</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>5850</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>5860</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46259.3125</v>
+        <v>46262.3125</v>
       </c>
       <c r="B32">
-        <v>5860</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46259.32291666666</v>
+        <v>46262.32291666666</v>
       </c>
       <c r="B33">
-        <v>5840</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46259.33333333334</v>
+        <v>46262.33333333334</v>
       </c>
       <c r="B34">
-        <v>5800</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46259.34375</v>
+        <v>46262.34375</v>
       </c>
       <c r="B35">
-        <v>5730</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46259.35416666666</v>
+        <v>46262.35416666666</v>
       </c>
       <c r="B36">
-        <v>5670</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46259.36458333334</v>
+        <v>46262.36458333334</v>
       </c>
       <c r="B37">
-        <v>5590</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46259.375</v>
+        <v>46262.375</v>
       </c>
       <c r="B38">
-        <v>5490</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46259.38541666666</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="B39">
-        <v>5410</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46259.39583333334</v>
+        <v>46262.39583333334</v>
       </c>
       <c r="B40">
-        <v>5340</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46259.40625</v>
+        <v>46262.40625</v>
       </c>
       <c r="B41">
-        <v>5280</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46259.41666666666</v>
+        <v>46262.41666666666</v>
       </c>
       <c r="B42">
-        <v>5230</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46259.42708333334</v>
+        <v>46262.42708333334</v>
       </c>
       <c r="B43">
-        <v>5200</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46259.4375</v>
+        <v>46262.4375</v>
       </c>
       <c r="B44">
-        <v>5190</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46259.44791666666</v>
+        <v>46262.44791666666</v>
       </c>
       <c r="B45">
-        <v>5180</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46259.45833333334</v>
+        <v>46262.45833333334</v>
       </c>
       <c r="B46">
-        <v>5130</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46259.46875</v>
+        <v>46262.46875</v>
       </c>
       <c r="B47">
-        <v>5130</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46259.47916666666</v>
+        <v>46262.47916666666</v>
       </c>
       <c r="B48">
-        <v>5130</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46259.48958333334</v>
+        <v>46262.48958333334</v>
       </c>
       <c r="B49">
-        <v>5150</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46259.5</v>
+        <v>46262.5</v>
       </c>
       <c r="B50">
-        <v>5250</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46259.51041666666</v>
+        <v>46262.51041666666</v>
       </c>
       <c r="B51">
-        <v>5290</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46259.52083333334</v>
+        <v>46262.52083333334</v>
       </c>
       <c r="B52">
-        <v>5310</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46259.53125</v>
+        <v>46262.53125</v>
       </c>
       <c r="B53">
-        <v>5350</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46259.54166666666</v>
+        <v>46262.54166666666</v>
       </c>
       <c r="B54">
-        <v>5370</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46259.55208333334</v>
+        <v>46262.55208333334</v>
       </c>
       <c r="B55">
-        <v>5380</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46259.5625</v>
+        <v>46262.5625</v>
       </c>
       <c r="B56">
-        <v>5380</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46259.57291666666</v>
+        <v>46262.57291666666</v>
       </c>
       <c r="B57">
-        <v>5400</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46259.58333333334</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="B58">
-        <v>5470</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46259.59375</v>
+        <v>46262.59375</v>
       </c>
       <c r="B59">
-        <v>5490</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46259.60416666666</v>
+        <v>46262.60416666666</v>
       </c>
       <c r="B60">
-        <v>5510</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46259.61458333334</v>
+        <v>46262.61458333334</v>
       </c>
       <c r="B61">
-        <v>5520</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46259.625</v>
+        <v>46262.625</v>
       </c>
       <c r="B62">
-        <v>5530</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46259.63541666666</v>
+        <v>46262.63541666666</v>
       </c>
       <c r="B63">
-        <v>5570</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46259.64583333334</v>
+        <v>46262.64583333334</v>
       </c>
       <c r="B64">
-        <v>5620</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46259.65625</v>
+        <v>46262.65625</v>
       </c>
       <c r="B65">
-        <v>5690</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46259.66666666666</v>
+        <v>46262.66666666666</v>
       </c>
       <c r="B66">
-        <v>5750</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46259.67708333334</v>
+        <v>46262.67708333334</v>
       </c>
       <c r="B67">
-        <v>5840</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46259.6875</v>
+        <v>46262.6875</v>
       </c>
       <c r="B68">
-        <v>5950</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46259.69791666666</v>
+        <v>46262.69791666666</v>
       </c>
       <c r="B69">
-        <v>6060</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46259.70833333334</v>
+        <v>46262.70833333334</v>
       </c>
       <c r="B70">
-        <v>6250</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46259.71875</v>
+        <v>46262.71875</v>
       </c>
       <c r="B71">
-        <v>6380</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46259.72916666666</v>
+        <v>46262.72916666666</v>
       </c>
       <c r="B72">
-        <v>6520</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46259.73958333334</v>
+        <v>46262.73958333334</v>
       </c>
       <c r="B73">
-        <v>6650</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46259.75</v>
+        <v>46262.75</v>
       </c>
       <c r="B74">
-        <v>6770</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46259.76041666666</v>
+        <v>46262.76041666666</v>
       </c>
       <c r="B75">
-        <v>6880</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46259.77083333334</v>
+        <v>46262.77083333334</v>
       </c>
       <c r="B76">
-        <v>6950</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46259.78125</v>
+        <v>46262.78125</v>
       </c>
       <c r="B77">
-        <v>7010</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46259.79166666666</v>
+        <v>46262.79166666666</v>
       </c>
       <c r="B78">
-        <v>7060</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46259.80208333334</v>
+        <v>46262.80208333334</v>
       </c>
       <c r="B79">
-        <v>7100</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46259.8125</v>
+        <v>46262.8125</v>
       </c>
       <c r="B80">
-        <v>7120</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46259.82291666666</v>
+        <v>46262.82291666666</v>
       </c>
       <c r="B81">
-        <v>7130</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46259.83333333334</v>
+        <v>46262.83333333334</v>
       </c>
       <c r="B82">
-        <v>7100</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46259.84375</v>
+        <v>46262.84375</v>
       </c>
       <c r="B83">
-        <v>7050</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46259.85416666666</v>
+        <v>46262.85416666666</v>
       </c>
       <c r="B84">
-        <v>6980</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46259.86458333334</v>
+        <v>46262.86458333334</v>
       </c>
       <c r="B85">
-        <v>6870</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46259.875</v>
+        <v>46262.875</v>
       </c>
       <c r="B86">
-        <v>6700</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46259.88541666666</v>
+        <v>46262.88541666666</v>
       </c>
       <c r="B87">
-        <v>6520</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46259.89583333334</v>
+        <v>46262.89583333334</v>
       </c>
       <c r="B88">
-        <v>6350</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46259.90625</v>
+        <v>46262.90625</v>
       </c>
       <c r="B89">
-        <v>6230</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46259.91666666666</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="B90">
-        <v>6150</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46259.92708333334</v>
+        <v>46262.92708333334</v>
       </c>
       <c r="B91">
-        <v>6040</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46259.9375</v>
+        <v>46262.9375</v>
       </c>
       <c r="B92">
-        <v>5940</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46259.94791666666</v>
+        <v>46262.94791666666</v>
       </c>
       <c r="B93">
-        <v>5840</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46259.95833333334</v>
+        <v>46262.95833333334</v>
       </c>
       <c r="B94">
-        <v>5500</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46259.96875</v>
+        <v>46262.96875</v>
       </c>
       <c r="B95">
-        <v>5440</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46259.97916666666</v>
+        <v>46262.97916666666</v>
       </c>
       <c r="B96">
-        <v>5390</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46259.98958333334</v>
+        <v>46262.98958333334</v>
       </c>
       <c r="B97">
-        <v>5330</v>
+        <v>5400</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,23 +394,23 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
-        <v>5340</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
-        <v>5290</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
         <v>5260</v>
@@ -418,559 +418,559 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
-        <v>5230</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
-        <v>5170</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
-        <v>5140</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
-        <v>5140</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
-        <v>5150</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
-        <v>5160</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
-        <v>5170</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
-        <v>5170</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
-        <v>5180</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
-        <v>5190</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
-        <v>5200</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
-        <v>5200</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
-        <v>5210</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
-        <v>5220</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
-        <v>5230</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
-        <v>5260</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
-        <v>5290</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
-        <v>5330</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
-        <v>5390</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
-        <v>5470</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>5570</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>5720</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>5810</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>5900</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>5970</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>6040</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>6060</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>6060</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>6040</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>5960</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
-        <v>5890</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>5790</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>5680</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>5540</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>5430</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>5320</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
-        <v>5230</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>5150</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>5090</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>5040</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
-        <v>5000</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
-        <v>4950</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
-        <v>4940</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46262.47916666666</v>
+        <v>46269.47916666666</v>
       </c>
       <c r="B48">
-        <v>4940</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46262.48958333334</v>
+        <v>46269.48958333334</v>
       </c>
       <c r="B49">
-        <v>4970</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46262.5</v>
+        <v>46269.5</v>
       </c>
       <c r="B50">
-        <v>5030</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46262.51041666666</v>
+        <v>46269.51041666666</v>
       </c>
       <c r="B51">
-        <v>5090</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46262.52083333334</v>
+        <v>46269.52083333334</v>
       </c>
       <c r="B52">
-        <v>5120</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46262.53125</v>
+        <v>46269.53125</v>
       </c>
       <c r="B53">
-        <v>5160</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46262.54166666666</v>
+        <v>46269.54166666666</v>
       </c>
       <c r="B54">
-        <v>5200</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46262.55208333334</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="B55">
-        <v>5230</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46262.5625</v>
+        <v>46269.5625</v>
       </c>
       <c r="B56">
-        <v>5260</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46262.57291666666</v>
+        <v>46269.57291666666</v>
       </c>
       <c r="B57">
-        <v>5270</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46262.58333333334</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="B58">
-        <v>5300</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46262.59375</v>
+        <v>46269.59375</v>
       </c>
       <c r="B59">
-        <v>5330</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46262.60416666666</v>
+        <v>46269.60416666666</v>
       </c>
       <c r="B60">
-        <v>5360</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46262.61458333334</v>
+        <v>46269.61458333334</v>
       </c>
       <c r="B61">
-        <v>5410</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46262.625</v>
+        <v>46269.625</v>
       </c>
       <c r="B62">
-        <v>5490</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46262.63541666666</v>
+        <v>46269.63541666666</v>
       </c>
       <c r="B63">
-        <v>5580</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46262.64583333334</v>
+        <v>46269.64583333334</v>
       </c>
       <c r="B64">
-        <v>5660</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46262.65625</v>
+        <v>46269.65625</v>
       </c>
       <c r="B65">
-        <v>5750</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46262.66666666666</v>
+        <v>46269.66666666666</v>
       </c>
       <c r="B66">
-        <v>5830</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46262.67708333334</v>
+        <v>46269.67708333334</v>
       </c>
       <c r="B67">
-        <v>5920</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46262.6875</v>
+        <v>46269.6875</v>
       </c>
       <c r="B68">
-        <v>6010</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46262.69791666666</v>
+        <v>46269.69791666666</v>
       </c>
       <c r="B69">
-        <v>6120</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46262.70833333334</v>
+        <v>46269.70833333334</v>
       </c>
       <c r="B70">
-        <v>6230</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46262.71875</v>
+        <v>46269.71875</v>
       </c>
       <c r="B71">
-        <v>6340</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46262.72916666666</v>
+        <v>46269.72916666666</v>
       </c>
       <c r="B72">
-        <v>6440</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46262.73958333334</v>
+        <v>46269.73958333334</v>
       </c>
       <c r="B73">
-        <v>6510</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46262.75</v>
+        <v>46269.75</v>
       </c>
       <c r="B74">
         <v>6580</v>
@@ -978,186 +978,186 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46262.76041666666</v>
+        <v>46269.76041666666</v>
       </c>
       <c r="B75">
-        <v>6630</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46262.77083333334</v>
+        <v>46269.77083333334</v>
       </c>
       <c r="B76">
-        <v>6670</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46262.78125</v>
+        <v>46269.78125</v>
       </c>
       <c r="B77">
-        <v>6720</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46262.79166666666</v>
+        <v>46269.79166666666</v>
       </c>
       <c r="B78">
-        <v>6750</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46262.80208333334</v>
+        <v>46269.80208333334</v>
       </c>
       <c r="B79">
-        <v>6760</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46262.8125</v>
+        <v>46269.8125</v>
       </c>
       <c r="B80">
-        <v>6750</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46262.82291666666</v>
+        <v>46269.82291666666</v>
       </c>
       <c r="B81">
-        <v>6740</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46262.83333333334</v>
+        <v>46269.83333333334</v>
       </c>
       <c r="B82">
-        <v>6720</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46262.84375</v>
+        <v>46269.84375</v>
       </c>
       <c r="B83">
-        <v>6680</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46262.85416666666</v>
+        <v>46269.85416666666</v>
       </c>
       <c r="B84">
-        <v>6610</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46262.86458333334</v>
+        <v>46269.86458333334</v>
       </c>
       <c r="B85">
-        <v>6510</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46262.875</v>
+        <v>46269.875</v>
       </c>
       <c r="B86">
-        <v>6340</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46262.88541666666</v>
+        <v>46269.88541666666</v>
       </c>
       <c r="B87">
-        <v>6160</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46262.89583333334</v>
+        <v>46269.89583333334</v>
       </c>
       <c r="B88">
-        <v>6010</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46262.90625</v>
+        <v>46269.90625</v>
       </c>
       <c r="B89">
-        <v>5890</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46262.91666666666</v>
+        <v>46269.91666666666</v>
       </c>
       <c r="B90">
-        <v>5800</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46262.92708333334</v>
+        <v>46269.92708333334</v>
       </c>
       <c r="B91">
-        <v>5740</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46262.9375</v>
+        <v>46269.9375</v>
       </c>
       <c r="B92">
-        <v>5700</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46262.94791666666</v>
+        <v>46269.94791666666</v>
       </c>
       <c r="B93">
-        <v>5640</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46262.95833333334</v>
+        <v>46269.95833333334</v>
       </c>
       <c r="B94">
-        <v>5590</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46262.96875</v>
+        <v>46269.96875</v>
       </c>
       <c r="B95">
-        <v>5550</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46262.97916666666</v>
+        <v>46269.97916666666</v>
       </c>
       <c r="B96">
-        <v>5490</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46262.98958333334</v>
+        <v>46269.98958333334</v>
       </c>
       <c r="B97">
-        <v>5400</v>
+        <v>5510</v>
       </c>
     </row>
   </sheetData>
